--- a/upload/DOC-20260706-WA0017.xlsx
+++ b/upload/DOC-20260706-WA0017.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Saves\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOUTEN\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ECA25AA-7C0C-4C4E-9844-3D76D0032DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DB7F57-2E84-4F27-9AF3-6D69D6C61CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{021CC775-6935-4F21-AFC2-E7E5CBA8BD2A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{021CC775-6935-4F21-AFC2-E7E5CBA8BD2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -112,8 +115,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="[$-40C]mmm\-yy;@"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.0\ _€_-;\-* #,##0.0\ _€_-;_-* &quot;-&quot;?\ _€_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="[$-40C]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0\ _€_-;\-* #,##0.0\ _€_-;_-* &quot;-&quot;?\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -218,26 +221,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,9 +261,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,7 +301,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -403,7 +407,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -545,7 +549,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -562,8 +566,9 @@
     <col min="4" max="4" width="12" hidden="1" customWidth="1"/>
     <col min="5" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="22" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -590,7 +595,7 @@
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>7228.0000000000027</v>
+        <v>7228.0000000000018</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
@@ -673,27 +678,27 @@
         <v>2.5901976307035831E-2</v>
       </c>
       <c r="E4" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="E4:E12" si="1">SUMIFS(P:P,$M:$M,$A4)*$D4</f>
         <v>8.3669900997051592</v>
       </c>
       <c r="F4" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="F4:F12" si="2">SUMIFS(Q:Q,$M:$M,$A4)*$D4</f>
         <v>7.4870719984026097</v>
       </c>
       <c r="G4" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="G4:G12" si="3">SUMIFS(R:R,$M:$M,$A4)*$D4</f>
         <v>7.8119213776956844</v>
       </c>
       <c r="H4" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="H4:H12" si="4">SUMIFS(S:S,$M:$M,$A4)*$D4</f>
         <v>10.208744841436342</v>
       </c>
       <c r="I4" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="I4:I12" si="5">SUMIFS(T:T,$M:$M,$A4)*$D4</f>
         <v>10.359870422237904</v>
       </c>
       <c r="J4" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A4)*$D4</f>
+        <f t="shared" ref="J4:J12" si="6">SUMIFS(U:U,$M:$M,$A4)*$D4</f>
         <v>12.598506362148891</v>
       </c>
       <c r="K4" s="15">
@@ -704,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <f>SUMIFS(C:C,A:A,M4)</f>
+        <f t="shared" ref="N4:N17" si="7">SUMIFS(C:C,A:A,M4)</f>
         <v>2253.496000000001</v>
       </c>
       <c r="O4" s="1">
@@ -712,27 +717,27 @@
         <v>5.4528217803921843E-2</v>
       </c>
       <c r="P4" s="8">
-        <f>$O4*P$2</f>
+        <f t="shared" ref="P4:U18" si="8">$O4*P$2</f>
         <v>323.02516227043299</v>
       </c>
       <c r="Q4" s="8">
-        <f>$O4*Q$2</f>
+        <f t="shared" si="8"/>
         <v>289.05408257858971</v>
       </c>
       <c r="R4" s="8">
-        <f>$O4*R$2</f>
+        <f t="shared" si="8"/>
         <v>301.59557267349169</v>
       </c>
       <c r="S4" s="8">
-        <f>$O4*S$2</f>
+        <f t="shared" si="8"/>
         <v>394.12995828674707</v>
       </c>
       <c r="T4" s="8">
-        <f>$O4*T$2</f>
+        <f t="shared" si="8"/>
         <v>399.96447759176669</v>
       </c>
       <c r="U4" s="8">
-        <f>$O4*U$2</f>
+        <f t="shared" si="8"/>
         <v>486.39170281098285</v>
       </c>
       <c r="V4" s="15">
@@ -755,70 +760,70 @@
         <v>1.2427357315034035E-2</v>
       </c>
       <c r="E5" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="1"/>
         <v>4.0143491132815212</v>
       </c>
       <c r="F5" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="2"/>
         <v>3.5921783675734891</v>
       </c>
       <c r="G5" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="3"/>
         <v>3.7480359462457957</v>
       </c>
       <c r="H5" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="4"/>
         <v>4.8979938201888658</v>
       </c>
       <c r="I5" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="5"/>
         <v>4.9705014763538085</v>
       </c>
       <c r="J5" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A5)*$D5</f>
+        <f t="shared" si="6"/>
         <v>6.0445634858999284</v>
       </c>
       <c r="K5" s="16">
-        <f t="shared" ref="K5:K68" si="1">SUM(C5:J5)</f>
+        <f t="shared" ref="K5:K68" si="9">SUM(C5:J5)</f>
         <v>55.28504956685839</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="2">
-        <f>SUMIFS(C:C,A:A,M5)</f>
+        <f t="shared" si="7"/>
         <v>1573.2650000000001</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="2">N5/$N$18</f>
+        <f t="shared" ref="O5:O17" si="10">N5/$N$18</f>
         <v>3.8068555073222703E-2</v>
       </c>
       <c r="P5" s="8">
-        <f>$O5*P$2</f>
+        <f t="shared" si="8"/>
         <v>225.51812025377129</v>
       </c>
       <c r="Q5" s="8">
-        <f>$O5*Q$2</f>
+        <f t="shared" si="8"/>
         <v>201.80141044315354</v>
       </c>
       <c r="R5" s="8">
-        <f>$O5*R$2</f>
+        <f t="shared" si="8"/>
         <v>210.55717810999477</v>
       </c>
       <c r="S5" s="8">
-        <f>$O5*S$2</f>
+        <f t="shared" si="8"/>
         <v>275.1595160692537</v>
       </c>
       <c r="T5" s="8">
-        <f>$O5*T$2</f>
+        <f t="shared" si="8"/>
         <v>279.23285146208855</v>
       </c>
       <c r="U5" s="8">
-        <f>$O5*U$2</f>
+        <f t="shared" si="8"/>
         <v>339.57151125314653</v>
       </c>
       <c r="V5" s="16">
-        <f t="shared" ref="V5:V17" si="3">SUM(P5:U5)</f>
+        <f t="shared" ref="V5:V17" si="11">SUM(P5:U5)</f>
         <v>1531.8405875914084</v>
       </c>
     </row>
@@ -837,70 +842,70 @@
         <v>6.9225771867356301E-5</v>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="1"/>
         <v>2.2361666190748745E-2</v>
       </c>
       <c r="F6" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="2"/>
         <v>2.0009991977913422E-2</v>
       </c>
       <c r="G6" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="3"/>
         <v>2.0878186310099814E-2</v>
       </c>
       <c r="H6" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="4"/>
         <v>2.7283950578449009E-2</v>
       </c>
       <c r="I6" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="5"/>
         <v>2.7687849680813982E-2</v>
       </c>
       <c r="J6" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A6)*$D6</f>
+        <f t="shared" si="6"/>
         <v>3.3670841056968062E-2</v>
       </c>
       <c r="K6" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.30796171156686042</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="2">
-        <f>SUMIFS(C:C,A:A,M6)</f>
+        <f t="shared" si="7"/>
         <v>7276.3171999999977</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.17606625842336637</v>
       </c>
       <c r="P6" s="8">
-        <f>$O6*P$2</f>
+        <f t="shared" si="8"/>
         <v>1043.0165149000225</v>
       </c>
       <c r="Q6" s="8">
-        <f>$O6*Q$2</f>
+        <f t="shared" si="8"/>
         <v>933.3272359022651</v>
       </c>
       <c r="R6" s="8">
-        <f>$O6*R$2</f>
+        <f t="shared" si="8"/>
         <v>973.82247533963937</v>
       </c>
       <c r="S6" s="8">
-        <f>$O6*S$2</f>
+        <f t="shared" si="8"/>
         <v>1272.6069158840921</v>
       </c>
       <c r="T6" s="8">
-        <f>$O6*T$2</f>
+        <f t="shared" si="8"/>
         <v>1291.4460055353923</v>
       </c>
       <c r="U6" s="8">
-        <f>$O6*U$2</f>
+        <f t="shared" si="8"/>
         <v>1570.5110251364281</v>
       </c>
       <c r="V6" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>7084.7301726978385</v>
       </c>
     </row>
@@ -919,70 +924,70 @@
         <v>0</v>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F7" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H7" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I7" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J7" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A7)*$D7</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K7" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>
       </c>
       <c r="N7" s="2">
-        <f>SUMIFS(C:C,A:A,M7)</f>
+        <f t="shared" si="7"/>
         <v>1422.9749999999999</v>
       </c>
       <c r="O7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>3.4431962927618083E-2</v>
       </c>
       <c r="P7" s="8">
-        <f>$O7*P$2</f>
+        <f t="shared" si="8"/>
         <v>203.97494838320952</v>
       </c>
       <c r="Q7" s="8">
-        <f>$O7*Q$2</f>
+        <f t="shared" si="8"/>
         <v>182.52383547930347</v>
       </c>
       <c r="R7" s="8">
-        <f>$O7*R$2</f>
+        <f t="shared" si="8"/>
         <v>190.44318695265562</v>
       </c>
       <c r="S7" s="8">
-        <f>$O7*S$2</f>
+        <f t="shared" si="8"/>
         <v>248.87422804082351</v>
       </c>
       <c r="T7" s="8">
-        <f>$O7*T$2</f>
+        <f t="shared" si="8"/>
         <v>252.55844807407863</v>
       </c>
       <c r="U7" s="8">
-        <f>$O7*U$2</f>
+        <f t="shared" si="8"/>
         <v>307.13310931435331</v>
       </c>
       <c r="V7" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1385.5077562444239</v>
       </c>
     </row>
@@ -1001,70 +1006,70 @@
         <v>3.7386354357851078E-3</v>
       </c>
       <c r="E8" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="1"/>
         <v>1.2076733183144754</v>
       </c>
       <c r="F8" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="2"/>
         <v>1.0806678359866704</v>
       </c>
       <c r="G8" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="3"/>
         <v>1.1275558952730187</v>
       </c>
       <c r="H8" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="4"/>
         <v>1.4735082283553389</v>
       </c>
       <c r="I8" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="5"/>
         <v>1.4953213689798577</v>
       </c>
       <c r="J8" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A8)*$D8</f>
+        <f t="shared" si="6"/>
         <v>1.8184412558009995</v>
       </c>
       <c r="K8" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>16.631906538146144</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="N8" s="2">
-        <f>SUMIFS(C:C,A:A,M8)</f>
+        <f t="shared" si="7"/>
         <v>1662.3029999999997</v>
       </c>
       <c r="O8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>4.0223022379499512E-2</v>
       </c>
       <c r="P8" s="8">
-        <f>$O8*P$2</f>
+        <f t="shared" si="8"/>
         <v>238.28118457615511</v>
       </c>
       <c r="Q8" s="8">
-        <f>$O8*Q$2</f>
+        <f t="shared" si="8"/>
         <v>213.22224163372692</v>
       </c>
       <c r="R8" s="8">
-        <f>$O8*R$2</f>
+        <f t="shared" si="8"/>
         <v>222.4735367810118</v>
       </c>
       <c r="S8" s="8">
-        <f>$O8*S$2</f>
+        <f t="shared" si="8"/>
         <v>290.73200575902246</v>
       </c>
       <c r="T8" s="8">
-        <f>$O8*T$2</f>
+        <f t="shared" si="8"/>
         <v>295.03586915362894</v>
       </c>
       <c r="U8" s="8">
-        <f>$O8*U$2</f>
+        <f t="shared" si="8"/>
         <v>358.78935962513566</v>
       </c>
       <c r="V8" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1618.5341975286808</v>
       </c>
     </row>
@@ -1079,74 +1084,74 @@
         <v>607.87199999999973</v>
       </c>
       <c r="D9" s="1">
-        <f>C9/C13</f>
-        <v>0.26974620767021529</v>
+        <v>0.24415231398763479</v>
       </c>
       <c r="E9" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A9)*$D9</f>
-        <v>87.134812504505206</v>
+        <f t="shared" si="1"/>
+        <v>78.867340844557432</v>
       </c>
       <c r="F9" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A9)*$D9</f>
-        <v>77.971242587167822</v>
+        <f t="shared" si="2"/>
+        <v>70.573223129135556</v>
       </c>
       <c r="G9" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A9)*$D9</f>
-        <v>81.35426197880119</v>
+        <f t="shared" si="3"/>
+        <v>73.635256956658864</v>
       </c>
       <c r="H9" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A9)*$D9</f>
-        <v>106.31506157707017</v>
+        <f t="shared" si="4"/>
+        <v>96.227741327559272</v>
       </c>
       <c r="I9" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A9)*$D9</f>
-        <v>107.88890103317787</v>
+        <f t="shared" si="5"/>
+        <v>97.652252716885343</v>
       </c>
       <c r="J9" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A9)*$D9</f>
-        <v>131.20231727552101</v>
+        <f t="shared" si="6"/>
+        <v>118.75365974568743</v>
       </c>
       <c r="K9" s="16">
-        <f t="shared" si="1"/>
-        <v>1200.0083431639132</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>1143.8256270344714</v>
+      </c>
+      <c r="L9" s="19"/>
       <c r="M9" s="11" t="s">
         <v>14</v>
       </c>
       <c r="N9" s="2">
-        <f>SUMIFS(C:C,A:A,M9)</f>
+        <f t="shared" si="7"/>
         <v>2043.5519999999997</v>
       </c>
       <c r="O9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>4.944816789097474E-2</v>
       </c>
       <c r="P9" s="8">
-        <f>$O9*P$2</f>
+        <f t="shared" si="8"/>
         <v>292.93094658613438</v>
       </c>
       <c r="Q9" s="8">
-        <f>$O9*Q$2</f>
+        <f t="shared" si="8"/>
         <v>262.1247379900571</v>
       </c>
       <c r="R9" s="8">
-        <f>$O9*R$2</f>
+        <f t="shared" si="8"/>
         <v>273.49781660498127</v>
       </c>
       <c r="S9" s="8">
-        <f>$O9*S$2</f>
+        <f t="shared" si="8"/>
         <v>357.41135751596539</v>
       </c>
       <c r="T9" s="8">
-        <f>$O9*T$2</f>
+        <f t="shared" si="8"/>
         <v>362.70231148029973</v>
       </c>
       <c r="U9" s="8">
-        <f>$O9*U$2</f>
+        <f t="shared" si="8"/>
         <v>441.07765758749468</v>
       </c>
       <c r="V9" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1989.7448277649323</v>
       </c>
     </row>
@@ -1161,74 +1166,73 @@
         <v>1550.6180000000008</v>
       </c>
       <c r="D10" s="1">
-        <f>C10/C13</f>
-        <v>0.68809440975266878</v>
+        <v>0.71368830343524947</v>
       </c>
       <c r="E10" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A10)*$D10</f>
-        <v>222.27180836773363</v>
+        <f t="shared" si="1"/>
+        <v>230.53928002768149</v>
       </c>
       <c r="F10" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A10)*$D10</f>
-        <v>198.89649833851388</v>
+        <f t="shared" si="2"/>
+        <v>206.29451779654619</v>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A10)*$D10</f>
-        <v>207.52622756278438</v>
+        <f t="shared" si="3"/>
+        <v>215.24523258492678</v>
       </c>
       <c r="H10" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A10)*$D10</f>
-        <v>271.19862101316318</v>
+        <f t="shared" si="4"/>
+        <v>281.28594126267416</v>
       </c>
       <c r="I10" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A10)*$D10</f>
-        <v>275.2133211305412</v>
+        <f t="shared" si="5"/>
+        <v>285.44996944683385</v>
       </c>
       <c r="J10" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A10)*$D10</f>
-        <v>334.68341165431872</v>
+        <f t="shared" si="6"/>
+        <v>347.13206918415239</v>
       </c>
       <c r="K10" s="16">
-        <f t="shared" si="1"/>
-        <v>3061.0959824768083</v>
+        <f t="shared" si="9"/>
+        <v>3117.2786986062506</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>15</v>
       </c>
       <c r="N10" s="2">
-        <f>SUMIFS(C:C,A:A,M10)</f>
+        <f t="shared" si="7"/>
         <v>3958.4668000000001</v>
       </c>
       <c r="O10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>9.5783680042029556E-2</v>
       </c>
       <c r="P10" s="8">
-        <f>$O10*P$2</f>
+        <f t="shared" si="8"/>
         <v>567.42252056898315</v>
       </c>
       <c r="Q10" s="8">
-        <f>$O10*Q$2</f>
+        <f t="shared" si="8"/>
         <v>507.7492879027987</v>
       </c>
       <c r="R10" s="8">
-        <f>$O10*R$2</f>
+        <f t="shared" si="8"/>
         <v>529.77953431246544</v>
       </c>
       <c r="S10" s="8">
-        <f>$O10*S$2</f>
+        <f t="shared" si="8"/>
         <v>692.32443934378966</v>
       </c>
       <c r="T10" s="8">
-        <f>$O10*T$2</f>
+        <f t="shared" si="8"/>
         <v>702.57329310828675</v>
       </c>
       <c r="U10" s="8">
-        <f>$O10*U$2</f>
+        <f t="shared" si="8"/>
         <v>854.39042597490368</v>
       </c>
       <c r="V10" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3854.239501211227</v>
       </c>
     </row>
@@ -1247,70 +1251,70 @@
         <v>0</v>
       </c>
       <c r="E11" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F11" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H11" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I11" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J11" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A11)*$D11</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K11" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="N11" s="2">
-        <f>SUMIFS(C:C,A:A,M11)</f>
+        <f t="shared" si="7"/>
         <v>1222.6189999999997</v>
       </c>
       <c r="O11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.958391544658303E-2</v>
       </c>
       <c r="P11" s="8">
-        <f>$O11*P$2</f>
+        <f t="shared" si="8"/>
         <v>175.25511510555788</v>
       </c>
       <c r="Q11" s="8">
-        <f>$O11*Q$2</f>
+        <f t="shared" si="8"/>
         <v>156.82433578233665</v>
       </c>
       <c r="R11" s="8">
-        <f>$O11*R$2</f>
+        <f t="shared" si="8"/>
         <v>163.62863633505074</v>
       </c>
       <c r="S11" s="8">
-        <f>$O11*S$2</f>
+        <f t="shared" si="8"/>
         <v>213.83254084790215</v>
       </c>
       <c r="T11" s="8">
-        <f>$O11*T$2</f>
+        <f t="shared" si="8"/>
         <v>216.99801980068654</v>
       </c>
       <c r="U11" s="8">
-        <f>$O11*U$2</f>
+        <f t="shared" si="8"/>
         <v>263.88852578352061</v>
       </c>
       <c r="V11" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1190.4271736550545</v>
       </c>
     </row>
@@ -1329,146 +1333,150 @@
         <v>2.2187747393383429E-5</v>
       </c>
       <c r="E12" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="1"/>
         <v>7.1672007021630589E-3</v>
       </c>
       <c r="F12" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="2"/>
         <v>6.4134589672799423E-3</v>
       </c>
       <c r="G12" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="3"/>
         <v>6.6917263814422479E-3</v>
       </c>
       <c r="H12" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="4"/>
         <v>8.7448559546310922E-3</v>
       </c>
       <c r="I12" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="5"/>
         <v>8.874310795132687E-3</v>
       </c>
       <c r="J12" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A12)*$D12</f>
+        <f t="shared" si="6"/>
         <v>1.0791936236207712E-2</v>
       </c>
       <c r="K12" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>9.8705676784250129E-2</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="N12" s="2">
-        <f>SUMIFS(C:C,A:A,M12)</f>
+        <f t="shared" si="7"/>
         <v>737.06999999999982</v>
       </c>
       <c r="O12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.7835005474487926E-2</v>
       </c>
       <c r="P12" s="8">
-        <f>$O12*P$2</f>
+        <f t="shared" si="8"/>
         <v>105.65457243086647</v>
       </c>
       <c r="Q12" s="8">
-        <f>$O12*Q$2</f>
+        <f t="shared" si="8"/>
         <v>94.543364020260498</v>
       </c>
       <c r="R12" s="8">
-        <f>$O12*R$2</f>
+        <f t="shared" si="8"/>
         <v>98.645415279392722</v>
       </c>
       <c r="S12" s="8">
-        <f>$O12*S$2</f>
+        <f t="shared" si="8"/>
         <v>128.91141956959873</v>
       </c>
       <c r="T12" s="8">
-        <f>$O12*T$2</f>
+        <f t="shared" si="8"/>
         <v>130.81976515536894</v>
       </c>
       <c r="U12" s="8">
-        <f>$O12*U$2</f>
+        <f t="shared" si="8"/>
         <v>159.0882488324323</v>
       </c>
       <c r="V12" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>717.66278528791963</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="19">
+        <f>1-D13</f>
+        <v>0</v>
+      </c>
       <c r="C13" s="3">
         <v>2253.496000000001</v>
       </c>
       <c r="D13" s="5">
         <f>SUM(D4:D12)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9">
         <f>SUM(E4:E12)</f>
-        <v>323.02516227043293</v>
+        <v>323.02516227043299</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" ref="F13:J13" si="4">SUM(F4:F12)</f>
-        <v>289.05408257858966</v>
+        <f t="shared" ref="F13:J13" si="12">SUM(F4:F12)</f>
+        <v>289.05408257858971</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" si="4"/>
-        <v>301.59557267349163</v>
+        <f t="shared" si="12"/>
+        <v>301.59557267349169</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" si="4"/>
-        <v>394.12995828674696</v>
+        <f t="shared" si="12"/>
+        <v>394.12995828674701</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="4"/>
-        <v>399.96447759176658</v>
+        <f t="shared" si="12"/>
+        <v>399.96447759176669</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="4"/>
-        <v>486.39170281098274</v>
+        <f t="shared" si="12"/>
+        <v>486.39170281098285</v>
       </c>
       <c r="K13" s="18">
-        <f t="shared" si="1"/>
-        <v>4448.6569562120112</v>
+        <f t="shared" si="9"/>
+        <v>4448.6569562120121</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>18</v>
       </c>
       <c r="N13" s="2">
-        <f>SUMIFS(C:C,A:A,M13)</f>
+        <f t="shared" si="7"/>
         <v>1122.6889999999996</v>
       </c>
       <c r="O13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.7165892603344829E-2</v>
       </c>
       <c r="P13" s="8">
-        <f>$O13*P$2</f>
+        <f t="shared" si="8"/>
         <v>160.93074778221478</v>
       </c>
       <c r="Q13" s="8">
-        <f>$O13*Q$2</f>
+        <f t="shared" si="8"/>
         <v>144.00639669033094</v>
       </c>
       <c r="R13" s="8">
-        <f>$O13*R$2</f>
+        <f t="shared" si="8"/>
         <v>150.25455198910026</v>
       </c>
       <c r="S13" s="8">
-        <f>$O13*S$2</f>
+        <f t="shared" si="8"/>
         <v>196.35507173697644</v>
       </c>
       <c r="T13" s="8">
-        <f>$O13*T$2</f>
+        <f t="shared" si="8"/>
         <v>199.26182224553432</v>
       </c>
       <c r="U13" s="8">
-        <f>$O13*U$2</f>
+        <f t="shared" si="8"/>
         <v>242.31976202183588</v>
       </c>
       <c r="V13" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1093.1283524659925</v>
       </c>
     </row>
@@ -1483,74 +1491,74 @@
         <v>30.924999999999997</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" ref="D14" si="5">C14/C23</f>
+        <f t="shared" ref="D14" si="13">C14/C23</f>
         <v>1.9656574067305886E-2</v>
       </c>
       <c r="E14" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="E14:E22" si="14">SUMIFS(P:P,$M:$M,$A14)*$D14</f>
         <v>4.4329136342878508</v>
       </c>
       <c r="F14" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="F14:F22" si="15">SUMIFS(Q:Q,$M:$M,$A14)*$D14</f>
         <v>3.966724371262643</v>
       </c>
       <c r="G14" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="G14:G22" si="16">SUMIFS(R:R,$M:$M,$A14)*$D14</f>
         <v>4.1388327669220297</v>
       </c>
       <c r="H14" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="H14:H22" si="17">SUMIFS(S:S,$M:$M,$A14)*$D14</f>
         <v>5.4086934079393298</v>
       </c>
       <c r="I14" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="I14:I22" si="18">SUMIFS(T:T,$M:$M,$A14)*$D14</f>
         <v>5.488761226789566</v>
       </c>
       <c r="J14" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A14)*$D14</f>
+        <f t="shared" ref="J14:J22" si="19">SUMIFS(U:U,$M:$M,$A14)*$D14</f>
         <v>6.6748125620944689</v>
       </c>
       <c r="K14" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>61.055394543363185</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>19</v>
       </c>
       <c r="N14" s="2">
-        <f>SUMIFS(C:C,A:A,M14)</f>
+        <f t="shared" si="7"/>
         <v>1689.5729999999983</v>
       </c>
       <c r="O14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>4.0882879108560879E-2</v>
       </c>
       <c r="P14" s="8">
-        <f>$O14*P$2</f>
+        <f t="shared" si="8"/>
         <v>242.19017583911466</v>
       </c>
       <c r="Q14" s="8">
-        <f>$O14*Q$2</f>
+        <f t="shared" si="8"/>
         <v>216.72014215448121</v>
       </c>
       <c r="R14" s="8">
-        <f>$O14*R$2</f>
+        <f t="shared" si="8"/>
         <v>226.12320434945022</v>
       </c>
       <c r="S14" s="8">
-        <f>$O14*S$2</f>
+        <f t="shared" si="8"/>
         <v>295.50145019667804</v>
       </c>
       <c r="T14" s="8">
-        <f>$O14*T$2</f>
+        <f t="shared" si="8"/>
         <v>299.87591826129403</v>
       </c>
       <c r="U14" s="8">
-        <f>$O14*U$2</f>
+        <f t="shared" si="8"/>
         <v>364.67528164836307</v>
       </c>
       <c r="V14" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1645.0861724493811</v>
       </c>
     </row>
@@ -1565,74 +1573,74 @@
         <v>16.629999999999956</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15" si="6">C15/C23</f>
+        <f t="shared" ref="D15" si="20">C15/C23</f>
         <v>1.0570374348885888E-2</v>
       </c>
       <c r="E15" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="14"/>
         <v>2.383810953539427</v>
       </c>
       <c r="F15" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="15"/>
         <v>2.133116452517303</v>
       </c>
       <c r="G15" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="16"/>
         <v>2.2256681944676857</v>
       </c>
       <c r="H15" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="17"/>
         <v>2.9085390905102937</v>
       </c>
       <c r="I15" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="18"/>
         <v>2.951595770461124</v>
       </c>
       <c r="J15" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A15)*$D15</f>
+        <f t="shared" si="19"/>
         <v>3.5893979921626755</v>
       </c>
       <c r="K15" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>32.832698828007352</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="N15" s="2">
-        <f>SUMIFS(C:C,A:A,M15)</f>
+        <f t="shared" si="7"/>
         <v>2387.0360000000001</v>
       </c>
       <c r="O15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>5.775950741150742E-2</v>
       </c>
       <c r="P15" s="8">
-        <f>$O15*P$2</f>
+        <f t="shared" si="8"/>
         <v>342.16732190576994</v>
       </c>
       <c r="Q15" s="8">
-        <f>$O15*Q$2</f>
+        <f t="shared" si="8"/>
         <v>306.18314878840084</v>
       </c>
       <c r="R15" s="8">
-        <f>$O15*R$2</f>
+        <f t="shared" si="8"/>
         <v>319.46783549304752</v>
       </c>
       <c r="S15" s="8">
-        <f>$O15*S$2</f>
+        <f t="shared" si="8"/>
         <v>417.48571957037564</v>
       </c>
       <c r="T15" s="8">
-        <f>$O15*T$2</f>
+        <f t="shared" si="8"/>
         <v>423.66598686340694</v>
       </c>
       <c r="U15" s="8">
-        <f>$O15*U$2</f>
+        <f t="shared" si="8"/>
         <v>515.21480611064624</v>
       </c>
       <c r="V15" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2324.1848187316473</v>
       </c>
     </row>
@@ -1647,74 +1655,74 @@
         <v>0.15000000000000002</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16" si="7">C16/C23</f>
+        <f t="shared" ref="D16" si="21">C16/C23</f>
         <v>9.534312401280141E-5</v>
       </c>
       <c r="E16" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="14"/>
         <v>2.1501602106489177E-2</v>
       </c>
       <c r="F16" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="15"/>
         <v>1.9240376901839825E-2</v>
       </c>
       <c r="G16" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="16"/>
         <v>2.0075179144326747E-2</v>
       </c>
       <c r="H16" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="17"/>
         <v>2.6234567863893277E-2</v>
       </c>
       <c r="I16" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="18"/>
         <v>2.6622932385398063E-2</v>
       </c>
       <c r="J16" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A16)*$D16</f>
+        <f t="shared" si="19"/>
         <v>3.2375808708623138E-2</v>
       </c>
       <c r="K16" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.29614581023458308</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>21</v>
       </c>
       <c r="N16" s="2">
-        <f>SUMIFS(C:C,A:A,M16)</f>
+        <f t="shared" si="7"/>
         <v>10790.921999999995</v>
       </c>
       <c r="O16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.2611097357710559</v>
       </c>
       <c r="P16" s="8">
-        <f>$O16*P$2</f>
+        <f t="shared" si="8"/>
         <v>1546.814074707735</v>
       </c>
       <c r="Q16" s="8">
-        <f>$O16*Q$2</f>
+        <f t="shared" si="8"/>
         <v>1384.1427093223674</v>
       </c>
       <c r="R16" s="8">
-        <f>$O16*R$2</f>
+        <f t="shared" si="8"/>
         <v>1444.1979485497102</v>
       </c>
       <c r="S16" s="8">
-        <f>$O16*S$2</f>
+        <f t="shared" si="8"/>
         <v>1887.3011701531921</v>
       </c>
       <c r="T16" s="8">
-        <f>$O16*T$2</f>
+        <f t="shared" si="8"/>
         <v>1915.239911880695</v>
       </c>
       <c r="U16" s="8">
-        <f>$O16*U$2</f>
+        <f t="shared" si="8"/>
         <v>2329.0988430778184</v>
       </c>
       <c r="V16" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>10506.794657691518</v>
       </c>
     </row>
@@ -1729,74 +1737,74 @@
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" ref="D17" si="8">C17/C23</f>
+        <f t="shared" ref="D17" si="22">C17/C23</f>
         <v>0</v>
       </c>
       <c r="E17" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F17" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H17" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I17" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J17" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A17)*$D17</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K17" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>22</v>
       </c>
       <c r="N17" s="2">
-        <f>SUMIFS(C:C,A:A,M17)</f>
+        <f t="shared" si="7"/>
         <v>3186.8690000000006</v>
       </c>
       <c r="O17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>7.7113199643827429E-2</v>
       </c>
       <c r="P17" s="8">
-        <f>$O17*P$2</f>
+        <f t="shared" si="8"/>
         <v>456.81859469003371</v>
       </c>
       <c r="Q17" s="8">
-        <f>$O17*Q$2</f>
+        <f t="shared" si="8"/>
         <v>408.77707131192921</v>
       </c>
       <c r="R17" s="8">
-        <f>$O17*R$2</f>
+        <f t="shared" si="8"/>
         <v>426.5131072300095</v>
       </c>
       <c r="S17" s="8">
-        <f>$O17*S$2</f>
+        <f t="shared" si="8"/>
         <v>557.37420702558461</v>
       </c>
       <c r="T17" s="8">
-        <f>$O17*T$2</f>
+        <f t="shared" si="8"/>
         <v>565.62531938747418</v>
       </c>
       <c r="U17" s="8">
-        <f>$O17*U$2</f>
+        <f t="shared" si="8"/>
         <v>687.8497408229407</v>
       </c>
       <c r="V17" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3102.9580404679718</v>
       </c>
     </row>
@@ -1811,35 +1819,35 @@
         <v>1.6750000000000003</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" ref="D18" si="9">C18/C23</f>
+        <f t="shared" ref="D18" si="23">C18/C23</f>
         <v>1.0646648848096159E-3</v>
       </c>
       <c r="E18" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="14"/>
         <v>0.24010122352246252</v>
       </c>
       <c r="F18" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="15"/>
         <v>0.21485087540387807</v>
       </c>
       <c r="G18" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="16"/>
         <v>0.22417283377831534</v>
       </c>
       <c r="H18" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="17"/>
         <v>0.29295267448014162</v>
       </c>
       <c r="I18" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="18"/>
         <v>0.29728941163694506</v>
       </c>
       <c r="J18" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A18)*$D18</f>
+        <f t="shared" si="19"/>
         <v>0.36152986391295844</v>
       </c>
       <c r="K18" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.3069615476195113</v>
       </c>
       <c r="N18" s="3">
@@ -1851,27 +1859,27 @@
         <v>1</v>
       </c>
       <c r="P18" s="9">
-        <f>$O18*P$2</f>
+        <f t="shared" si="8"/>
         <v>5924</v>
       </c>
       <c r="Q18" s="9">
-        <f>$O18*Q$2</f>
+        <f t="shared" si="8"/>
         <v>5301</v>
       </c>
       <c r="R18" s="9">
-        <f>$O18*R$2</f>
+        <f t="shared" si="8"/>
         <v>5531</v>
       </c>
       <c r="S18" s="9">
-        <f>$O18*S$2</f>
+        <f t="shared" si="8"/>
         <v>7228</v>
       </c>
       <c r="T18" s="9">
-        <f>$O18*T$2</f>
+        <f t="shared" si="8"/>
         <v>7335</v>
       </c>
       <c r="U18" s="9">
-        <f>$O18*U$2</f>
+        <f t="shared" si="8"/>
         <v>8920</v>
       </c>
       <c r="V18" s="18">
@@ -1890,37 +1898,37 @@
         <v>317.53999999999996</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" ref="D19" si="10">C19/C23</f>
-        <v>0.20183503732683303</v>
+        <v>0.23676542715014648</v>
       </c>
       <c r="E19" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A19)*$D19</f>
-        <v>45.517458219297147</v>
+        <f t="shared" si="14"/>
+        <v>53.394894071982257</v>
       </c>
       <c r="F19" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A19)*$D19</f>
-        <v>40.73059520940145</v>
+        <f t="shared" si="15"/>
+        <v>47.779597143075279</v>
       </c>
       <c r="G19" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A19)*$D19</f>
-        <v>42.497815903263422</v>
+        <f t="shared" si="16"/>
+        <v>49.852660214742386</v>
       </c>
       <c r="H19" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A19)*$D19</f>
-        <v>55.53683119667113</v>
+        <f t="shared" si="17"/>
+        <v>65.14826035656445</v>
       </c>
       <c r="I19" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A19)*$D19</f>
-        <v>56.358972997728664</v>
+        <f t="shared" si="18"/>
+        <v>66.112685350774797</v>
       </c>
       <c r="J19" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A19)*$D19</f>
-        <v>68.537428648907934</v>
+        <f t="shared" si="19"/>
+        <v>80.398793909872012</v>
       </c>
       <c r="K19" s="16">
-        <f t="shared" si="1"/>
-        <v>626.92093721259653</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>680.46365647416133</v>
+      </c>
+      <c r="L19" s="19"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
@@ -1933,36 +1941,35 @@
         <v>1206.3250000000003</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" ref="D20" si="11">C20/C23</f>
-        <v>0.76676529383161784</v>
+        <v>0.73183490400830431</v>
       </c>
       <c r="E20" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A20)*$D20</f>
-        <v>172.91946774073708</v>
+        <f t="shared" si="14"/>
+        <v>165.04203188805192</v>
       </c>
       <c r="F20" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A20)*$D20</f>
-        <v>154.73431777407953</v>
+        <f t="shared" si="15"/>
+        <v>147.68531584040568</v>
       </c>
       <c r="G20" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A20)*$D20</f>
-        <v>161.44793654186643</v>
+        <f t="shared" si="16"/>
+        <v>154.09309223038744</v>
       </c>
       <c r="H20" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A20)*$D20</f>
-        <v>210.98276718940707</v>
+        <f t="shared" si="17"/>
+        <v>201.37133802951374</v>
       </c>
       <c r="I20" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A20)*$D20</f>
-        <v>214.10605939876882</v>
+        <f t="shared" si="18"/>
+        <v>204.35234704572267</v>
       </c>
       <c r="J20" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A20)*$D20</f>
-        <v>260.37164960286543</v>
+        <f t="shared" si="19"/>
+        <v>248.51028434190133</v>
       </c>
       <c r="K20" s="16">
-        <f t="shared" si="1"/>
-        <v>2381.6539635415565</v>
+        <f t="shared" si="9"/>
+        <v>2328.1112442799913</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -1976,35 +1983,35 @@
         <v>0</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21" si="12">C21/C23</f>
+        <f t="shared" ref="D21" si="24">C21/C23</f>
         <v>0</v>
       </c>
       <c r="E21" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F21" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I21" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J21" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A21)*$D21</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K21" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -2019,72 +2026,76 @@
         <v>0.02</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" ref="D22" si="13">C22/C23</f>
+        <f t="shared" ref="D22" si="25">C22/C23</f>
         <v>1.2712416535040187E-5</v>
       </c>
       <c r="E22" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="14"/>
         <v>2.8668802808652235E-3</v>
       </c>
       <c r="F22" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="15"/>
         <v>2.5653835869119766E-3</v>
       </c>
       <c r="G22" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="16"/>
         <v>2.676690552576899E-3</v>
       </c>
       <c r="H22" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="17"/>
         <v>3.4979423818524368E-3</v>
       </c>
       <c r="I22" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="18"/>
         <v>3.549724318053075E-3</v>
       </c>
       <c r="J22" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A22)*$D22</f>
+        <f t="shared" si="19"/>
         <v>4.3167744944830845E-3</v>
       </c>
       <c r="K22" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.9486108031277736E-2</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="19">
+        <f>1-D23</f>
+        <v>0</v>
+      </c>
       <c r="C23" s="3">
         <v>1573.2650000000001</v>
       </c>
       <c r="D23" s="5">
-        <f t="shared" ref="D23:E23" si="14">SUM(D14:D22)</f>
+        <f t="shared" ref="D23:E23" si="26">SUM(D14:D22)</f>
         <v>1</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="14"/>
-        <v>225.51812025377131</v>
+        <f t="shared" si="26"/>
+        <v>225.51812025377126</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" ref="F23" si="15">SUM(F14:F22)</f>
-        <v>201.80141044315354</v>
+        <f t="shared" ref="F23" si="27">SUM(F14:F22)</f>
+        <v>201.80141044315351</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" ref="G23" si="16">SUM(G14:G22)</f>
-        <v>210.55717810999479</v>
+        <f t="shared" ref="G23" si="28">SUM(G14:G22)</f>
+        <v>210.55717810999477</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23" si="17">SUM(H14:H22)</f>
+        <f t="shared" ref="H23" si="29">SUM(H14:H22)</f>
         <v>275.1595160692537</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23" si="18">SUM(I14:I22)</f>
-        <v>279.2328514620886</v>
+        <f t="shared" ref="I23" si="30">SUM(I14:I22)</f>
+        <v>279.23285146208855</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" ref="J23" si="19">SUM(J14:J22)</f>
-        <v>339.57151125314658</v>
+        <f t="shared" ref="J23" si="31">SUM(J14:J22)</f>
+        <v>339.57151125314653</v>
       </c>
       <c r="K23" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3106.1055875914085</v>
       </c>
     </row>
@@ -2099,35 +2110,35 @@
         <v>67.630000000000038</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" ref="D24" si="20">C24/C33</f>
+        <f t="shared" ref="D24" si="32">C24/C33</f>
         <v>9.294537077080705E-3</v>
       </c>
       <c r="E24" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A24)*$D24</f>
+        <f t="shared" ref="E24:J28" si="33">SUMIFS(P:P,$M:$M,$A24)*$D24</f>
         <v>9.6943556697457591</v>
       </c>
       <c r="F24" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A24)*$D24</f>
+        <f t="shared" si="33"/>
         <v>8.6748445991428529</v>
       </c>
       <c r="G24" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A24)*$D24</f>
+        <f t="shared" si="33"/>
         <v>9.0512291035387893</v>
       </c>
       <c r="H24" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A24)*$D24</f>
+        <f t="shared" si="33"/>
         <v>11.82829216423402</v>
       </c>
       <c r="I24" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A24)*$D24</f>
+        <f t="shared" si="33"/>
         <v>12.003392781496476</v>
       </c>
       <c r="J24" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A24)*$D24</f>
+        <f t="shared" si="33"/>
         <v>14.597172953094558</v>
       </c>
       <c r="K24" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>133.48858180832957</v>
       </c>
     </row>
@@ -2142,35 +2153,35 @@
         <v>75.44720000000008</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" ref="D25" si="21">C25/C33</f>
+        <f t="shared" ref="D25" si="34">C25/C33</f>
         <v>1.0368871769361581E-2</v>
       </c>
       <c r="E25" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>10.814904496324747</v>
       </c>
       <c r="F25" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>9.6775504279232738</v>
       </c>
       <c r="G25" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>10.097440372919001</v>
       </c>
       <c r="H25" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>13.195497923604872</v>
       </c>
       <c r="I25" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>13.390838028450709</v>
       </c>
       <c r="J25" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A25)*$D25</f>
+        <f t="shared" si="33"/>
         <v>16.284427432008226</v>
       </c>
       <c r="K25" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>148.91822755300026</v>
       </c>
     </row>
@@ -2185,35 +2196,35 @@
         <v>0.14300000000000002</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26" si="22">C26/C33</f>
+        <f t="shared" ref="D26" si="35">C26/C33</f>
         <v>1.9652799083580366E-5</v>
       </c>
       <c r="E26" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>2.0498194008186348E-2</v>
       </c>
       <c r="F26" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>1.8342492646420631E-2</v>
       </c>
       <c r="G26" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>1.9138337450924827E-2</v>
       </c>
       <c r="H26" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>2.5010288030244923E-2</v>
       </c>
       <c r="I26" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>2.5380528874079482E-2</v>
       </c>
       <c r="J26" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A26)*$D26</f>
+        <f t="shared" si="33"/>
         <v>3.0864937635554056E-2</v>
       </c>
       <c r="K26" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.28225443144449386</v>
       </c>
     </row>
@@ -2228,35 +2239,35 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" ref="D27" si="23">C27/C33</f>
+        <f t="shared" ref="D27" si="36">C27/C33</f>
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="F27" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H27" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="I27" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J27" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A27)*$D27</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K27" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -2271,35 +2282,35 @@
         <v>32.000000000000007</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" ref="D28" si="24">C28/C33</f>
+        <f t="shared" ref="D28" si="37">C28/C33</f>
         <v>4.397829165556446E-3</v>
       </c>
       <c r="E28" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>4.5870084493843581</v>
       </c>
       <c r="F28" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>4.1046137390591628</v>
       </c>
       <c r="G28" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>4.2827048841230386</v>
       </c>
       <c r="H28" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>5.596707810963899</v>
       </c>
       <c r="I28" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>5.6795589088849194</v>
       </c>
       <c r="J28" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A28)*$D28</f>
+        <f t="shared" si="33"/>
         <v>6.9068391911729359</v>
       </c>
       <c r="K28" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>63.161830812753877</v>
       </c>
     </row>
@@ -2314,8 +2325,7 @@
         <v>838.51499999999942</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" ref="D29" si="25">C29/C33</f>
-        <v>0.11523892883614251</v>
+        <v>0.16769286142647954</v>
       </c>
       <c r="E29" s="8">
         <v>219.03346812900475</v>
@@ -2336,9 +2346,10 @@
         <v>329.80731527864987</v>
       </c>
       <c r="K29" s="16">
-        <f t="shared" si="1"/>
-        <v>2326.423575195382</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>2326.4760291279717</v>
+      </c>
+      <c r="L29" s="19"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
@@ -2351,8 +2362,7 @@
         <v>4362.6969999999983</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" ref="D30" si="26">C30/C33</f>
-        <v>0.59957487834642498</v>
+        <v>0.54712094575608794</v>
       </c>
       <c r="E30" s="8">
         <v>797.86627996155482</v>
@@ -2373,8 +2383,8 @@
         <v>1201.884405343867</v>
       </c>
       <c r="K30" s="16">
-        <f t="shared" si="1"/>
-        <v>9783.6267975949195</v>
+        <f t="shared" si="9"/>
+        <v>9783.5743436623306</v>
       </c>
       <c r="M30" s="6"/>
     </row>
@@ -2389,35 +2399,35 @@
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" ref="D31" si="27">C31/C33</f>
+        <f t="shared" ref="D31" si="38">C31/C33</f>
         <v>0</v>
       </c>
       <c r="E31" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A31)*$D31</f>
+        <f t="shared" ref="E31:J31" si="39">SUMIFS(P:P,$M:$M,$A31)*$D31</f>
         <v>0</v>
       </c>
       <c r="F31" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A31)*$D31</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A31)*$D31</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H31" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A31)*$D31</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="I31" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A31)*$D31</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="J31" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A31)*$D31</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K31" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -2432,7 +2442,7 @@
         <v>1899.885</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" ref="D32" si="28">C32/C33</f>
+        <f t="shared" ref="D32" si="40">C32/C33</f>
         <v>0.26110530200635024</v>
       </c>
       <c r="E32" s="8">
@@ -2454,48 +2464,52 @@
         <v>1</v>
       </c>
       <c r="K32" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>1906.1461053020064</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="19">
+        <f>1-D33</f>
+        <v>0</v>
+      </c>
       <c r="C33" s="3">
         <v>7276.3171999999977</v>
       </c>
       <c r="D33" s="5">
-        <f t="shared" ref="D33:E33" si="29">SUM(D24:D32)</f>
+        <f t="shared" ref="D33:E33" si="41">SUM(D24:D32)</f>
         <v>1</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>1043.0165149000227</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" ref="F33" si="30">SUM(F24:F32)</f>
+        <f t="shared" ref="F33" si="42">SUM(F24:F32)</f>
         <v>933.3272359022651</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33" si="31">SUM(G24:G32)</f>
+        <f t="shared" ref="G33" si="43">SUM(G24:G32)</f>
         <v>973.82247533963925</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33" si="32">SUM(H24:H32)</f>
+        <f t="shared" ref="H33" si="44">SUM(H24:H32)</f>
         <v>1272.6069158840924</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" ref="I33" si="33">SUM(I24:I32)</f>
+        <f t="shared" ref="I33" si="45">SUM(I24:I32)</f>
         <v>1291.4460055353925</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" ref="J33" si="34">SUM(J24:J32)</f>
+        <f t="shared" ref="J33" si="46">SUM(J24:J32)</f>
         <v>1570.5110251364281</v>
       </c>
       <c r="K33" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>14362.047372697836</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>12</v>
       </c>
@@ -2506,39 +2520,39 @@
         <v>26.160000000000004</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" ref="D34" si="35">C34/C43</f>
+        <f t="shared" ref="D34" si="47">C34/C43</f>
         <v>1.8384019395983772E-2</v>
       </c>
       <c r="E34" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="E34:E42" si="48">SUMIFS(P:P,$M:$M,$A34)*$D34</f>
         <v>3.7498794073717123</v>
       </c>
       <c r="F34" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="F34:F42" si="49">SUMIFS(Q:Q,$M:$M,$A34)*$D34</f>
         <v>3.3555217316808661</v>
       </c>
       <c r="G34" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="G34:G42" si="50">SUMIFS(R:R,$M:$M,$A34)*$D34</f>
         <v>3.5011112427705844</v>
       </c>
       <c r="H34" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="H34:H42" si="51">SUMIFS(S:S,$M:$M,$A34)*$D34</f>
         <v>4.5753086354629877</v>
       </c>
       <c r="I34" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="I34:I42" si="52">SUMIFS(T:T,$M:$M,$A34)*$D34</f>
         <v>4.6430394080134221</v>
       </c>
       <c r="J34" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A34)*$D34</f>
+        <f t="shared" ref="J34:J42" si="53">SUMIFS(U:U,$M:$M,$A34)*$D34</f>
         <v>5.6463410387838753</v>
       </c>
       <c r="K34" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>51.649585483479434</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>12</v>
       </c>
@@ -2549,39 +2563,39 @@
         <v>13.23599999999999</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35" si="36">C35/C43</f>
+        <f t="shared" ref="D35" si="54">C35/C43</f>
         <v>9.3016391714541655E-3</v>
       </c>
       <c r="E35" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="48"/>
         <v>1.8973013698766032</v>
       </c>
       <c r="F35" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="49"/>
         <v>1.6977708578183448</v>
       </c>
       <c r="G35" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="50"/>
         <v>1.7714338076953904</v>
       </c>
       <c r="H35" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="51"/>
         <v>2.3149382683099406</v>
       </c>
       <c r="I35" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="52"/>
         <v>2.3492075536875228</v>
       </c>
       <c r="J35" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A35)*$D35</f>
+        <f t="shared" si="53"/>
         <v>2.8568413604489029</v>
       </c>
       <c r="K35" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>26.132794857008154</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>12</v>
       </c>
@@ -2592,39 +2606,39 @@
         <v>0.12400000000000003</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" ref="D36" si="37">C36/C43</f>
+        <f t="shared" ref="D36" si="55">C36/C43</f>
         <v>8.7141376341819102E-5</v>
       </c>
       <c r="E36" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="48"/>
         <v>1.7774657741364386E-2</v>
       </c>
       <c r="F36" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="49"/>
         <v>1.5905378238854257E-2</v>
       </c>
       <c r="G36" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="50"/>
         <v>1.6595481425976777E-2</v>
       </c>
       <c r="H36" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="51"/>
         <v>2.1687242767485109E-2</v>
       </c>
       <c r="I36" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="52"/>
         <v>2.2008290771929062E-2</v>
       </c>
       <c r="J36" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A36)*$D36</f>
+        <f t="shared" si="53"/>
         <v>2.6764001865795126E-2</v>
       </c>
       <c r="K36" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.24482219418774659</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>12</v>
       </c>
@@ -2635,39 +2649,39 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" ref="D37" si="38">C37/C43</f>
+        <f t="shared" ref="D37" si="56">C37/C43</f>
         <v>0</v>
       </c>
       <c r="E37" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="F37" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="G37" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H37" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I37" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="J37" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A37)*$D37</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="K37" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>12</v>
       </c>
@@ -2678,39 +2692,39 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" ref="D38" si="39">C38/C43</f>
+        <f t="shared" ref="D38" si="57">C38/C43</f>
         <v>0</v>
       </c>
       <c r="E38" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="F38" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="G38" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H38" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I38" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="J38" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A38)*$D38</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="K38" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>12</v>
       </c>
@@ -2721,39 +2735,39 @@
         <v>305.69999999999993</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" ref="D39" si="40">C39/C43</f>
-        <v>0.21483160280398458</v>
+        <v>0.30593295950847316</v>
       </c>
       <c r="E39" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A39)*$D39</f>
-        <v>43.820265093024922</v>
+        <f t="shared" si="48"/>
+        <v>62.40265962446334</v>
       </c>
       <c r="F39" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A39)*$D39</f>
-        <v>39.21188812594955</v>
+        <f t="shared" si="49"/>
+        <v>55.840057169020966</v>
       </c>
       <c r="G39" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A39)*$D39</f>
-        <v>40.91321509613789</v>
+        <f t="shared" si="50"/>
+        <v>58.262847802651379</v>
       </c>
       <c r="H39" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A39)*$D39</f>
-        <v>53.46604930661448</v>
+        <f t="shared" si="51"/>
+        <v>76.138829129915777</v>
       </c>
       <c r="I39" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A39)*$D39</f>
-        <v>54.257536201441226</v>
+        <f t="shared" si="52"/>
+        <v>77.265953468169911</v>
       </c>
       <c r="J39" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A39)*$D39</f>
-        <v>65.981898148173926</v>
+        <f t="shared" si="53"/>
+        <v>93.962141095579511</v>
       </c>
       <c r="K39" s="16">
-        <f t="shared" si="1"/>
-        <v>603.56568357414596</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>729.87842124930921</v>
+      </c>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>12</v>
       </c>
@@ -2764,39 +2778,38 @@
         <v>1077.75</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" ref="D40" si="41">C40/C43</f>
-        <v>0.75739208348706066</v>
+        <v>0.66629072678257195</v>
       </c>
       <c r="E40" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A40)*$D40</f>
-        <v>154.48901113512471</v>
+        <f t="shared" si="48"/>
+        <v>135.90661660368627</v>
       </c>
       <c r="F40" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A40)*$D40</f>
-        <v>138.24210803971914</v>
+        <f t="shared" si="49"/>
+        <v>121.6139389966477</v>
       </c>
       <c r="G40" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A40)*$D40</f>
-        <v>144.24016215198765</v>
+        <f t="shared" si="50"/>
+        <v>126.89052944547414</v>
       </c>
       <c r="H40" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A40)*$D40</f>
-        <v>188.49537010207317</v>
+        <f t="shared" si="51"/>
+        <v>165.82259027877186</v>
       </c>
       <c r="I40" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A40)*$D40</f>
-        <v>191.28576918908504</v>
+        <f t="shared" si="52"/>
+        <v>168.2773519223563</v>
       </c>
       <c r="J40" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A40)*$D40</f>
-        <v>232.6201855714572</v>
+        <f t="shared" si="53"/>
+        <v>204.63994262405157</v>
       </c>
       <c r="K40" s="16">
-        <f t="shared" si="1"/>
-        <v>2127.8799982729338</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>2001.5672605977704</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>12</v>
       </c>
@@ -2807,39 +2820,39 @@
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" ref="D41" si="42">C41/C43</f>
+        <f t="shared" ref="D41" si="58">C41/C43</f>
         <v>0</v>
       </c>
       <c r="E41" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="F41" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="G41" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H41" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I41" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="J41" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A41)*$D41</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="K41" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>12</v>
       </c>
@@ -2850,76 +2863,80 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" ref="D42" si="43">C42/C43</f>
+        <f t="shared" ref="D42" si="59">C42/C43</f>
         <v>3.5137651750733502E-6</v>
       </c>
       <c r="E42" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="48"/>
         <v>7.1672007021630576E-4</v>
       </c>
       <c r="F42" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="49"/>
         <v>6.4134589672799414E-4</v>
       </c>
       <c r="G42" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="50"/>
         <v>6.6917263814422474E-4</v>
       </c>
       <c r="H42" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="51"/>
         <v>8.7448559546310909E-4</v>
       </c>
       <c r="I42" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="52"/>
         <v>8.8743107951326852E-4</v>
       </c>
       <c r="J42" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A42)*$D42</f>
+        <f t="shared" si="53"/>
         <v>1.0791936236207711E-3</v>
       </c>
       <c r="K42" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>9.8718626688607466E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="19">
+        <f>1-D43</f>
+        <v>0</v>
+      </c>
       <c r="C43" s="3">
         <v>1422.9749999999999</v>
       </c>
       <c r="D43" s="5">
-        <f t="shared" ref="D43:E43" si="44">SUM(D34:D42)</f>
-        <v>1</v>
+        <f t="shared" ref="D43:E43" si="60">SUM(D34:D42)</f>
+        <v>0.99999999999999989</v>
       </c>
       <c r="E43" s="9">
-        <f t="shared" si="44"/>
-        <v>203.97494838320952</v>
+        <f t="shared" si="60"/>
+        <v>203.97494838320949</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" ref="F43" si="45">SUM(F34:F42)</f>
-        <v>182.52383547930347</v>
+        <f t="shared" ref="F43" si="61">SUM(F34:F42)</f>
+        <v>182.52383547930344</v>
       </c>
       <c r="G43" s="9">
-        <f t="shared" ref="G43" si="46">SUM(G34:G42)</f>
+        <f t="shared" ref="G43" si="62">SUM(G34:G42)</f>
         <v>190.44318695265562</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" ref="H43" si="47">SUM(H34:H42)</f>
+        <f t="shared" ref="H43" si="63">SUM(H34:H42)</f>
         <v>248.87422804082351</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" ref="I43" si="48">SUM(I34:I42)</f>
-        <v>252.55844807407865</v>
+        <f t="shared" ref="I43" si="64">SUM(I34:I42)</f>
+        <v>252.5584480740786</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" ref="J43" si="49">SUM(J34:J42)</f>
-        <v>307.13310931435336</v>
+        <f t="shared" ref="J43" si="65">SUM(J34:J42)</f>
+        <v>307.13310931435331</v>
       </c>
       <c r="K43" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2809.4827562444243</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>13</v>
       </c>
@@ -2930,39 +2947,39 @@
         <v>22.779999999999987</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" ref="D44" si="50">C44/C53</f>
+        <f t="shared" ref="D44" si="66">C44/C53</f>
         <v>1.3703879497299825E-2</v>
       </c>
       <c r="E44" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="E44:E52" si="67">SUMIFS(P:P,$M:$M,$A44)*$D44</f>
         <v>3.2653766399054875</v>
       </c>
       <c r="F44" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="F44:F52" si="68">SUMIFS(Q:Q,$M:$M,$A44)*$D44</f>
         <v>2.9219719054927396</v>
       </c>
       <c r="G44" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="G44:G52" si="69">SUMIFS(R:R,$M:$M,$A44)*$D44</f>
         <v>3.048750539385086</v>
       </c>
       <c r="H44" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="H44:H52" si="70">SUMIFS(S:S,$M:$M,$A44)*$D44</f>
         <v>3.9841563729299225</v>
       </c>
       <c r="I44" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="I44:I52" si="71">SUMIFS(T:T,$M:$M,$A44)*$D44</f>
         <v>4.0431359982624491</v>
       </c>
       <c r="J44" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A44)*$D44</f>
+        <f t="shared" ref="J44:J52" si="72">SUMIFS(U:U,$M:$M,$A44)*$D44</f>
         <v>4.9168061492162298</v>
       </c>
       <c r="K44" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>44.9739014846892</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>13</v>
       </c>
@@ -2973,39 +2990,39 @@
         <v>27.187999999999967</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" ref="D45" si="51">C45/C53</f>
+        <f t="shared" ref="D45" si="73">C45/C53</f>
         <v>1.6355622290280397E-2</v>
       </c>
       <c r="E45" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="67"/>
         <v>3.8972370538081802</v>
       </c>
       <c r="F45" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="68"/>
         <v>3.487382448048137</v>
       </c>
       <c r="G45" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="69"/>
         <v>3.6386931371730324</v>
       </c>
       <c r="H45" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="70"/>
         <v>4.7551028738901966</v>
       </c>
       <c r="I45" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="71"/>
         <v>4.8254952379613441</v>
       </c>
       <c r="J45" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A45)*$D45</f>
+        <f t="shared" si="72"/>
         <v>5.868223247800298</v>
       </c>
       <c r="K45" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>53.676489620971438</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>13</v>
       </c>
@@ -3016,39 +3033,39 @@
         <v>0.28600000000000009</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" ref="D46" si="52">C46/C53</f>
+        <f t="shared" ref="D46" si="74">C46/C53</f>
         <v>1.7205046252097251E-4</v>
       </c>
       <c r="E46" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="67"/>
         <v>4.099638801637271E-2</v>
       </c>
       <c r="F46" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="68"/>
         <v>3.6684985292841275E-2</v>
       </c>
       <c r="G46" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="69"/>
         <v>3.8276674901849668E-2</v>
       </c>
       <c r="H46" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="70"/>
         <v>5.002057606048986E-2</v>
       </c>
       <c r="I46" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="71"/>
         <v>5.0761057748158984E-2</v>
       </c>
       <c r="J46" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A46)*$D46</f>
+        <f t="shared" si="72"/>
         <v>6.1729875271108132E-2</v>
       </c>
       <c r="K46" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.56464160775334171</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>13</v>
       </c>
@@ -3059,39 +3076,39 @@
         <v>0</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" ref="D47" si="53">C47/C53</f>
+        <f t="shared" ref="D47" si="75">C47/C53</f>
         <v>0</v>
       </c>
       <c r="E47" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F47" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G47" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="H47" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="I47" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="J47" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A47)*$D47</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K47" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>13</v>
       </c>
@@ -3102,39 +3119,39 @@
         <v>2.1</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="54">C48/C53</f>
+        <f t="shared" ref="D48" si="76">C48/C53</f>
         <v>1.2633075919372104E-3</v>
       </c>
       <c r="E48" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="67"/>
         <v>0.30102242949084845</v>
       </c>
       <c r="F48" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="68"/>
         <v>0.26936527662575754</v>
       </c>
       <c r="G48" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="69"/>
         <v>0.28105250802057441</v>
       </c>
       <c r="H48" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="70"/>
         <v>0.36728395009450582</v>
       </c>
       <c r="I48" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="71"/>
         <v>0.37272105339557288</v>
       </c>
       <c r="J48" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A48)*$D48</f>
+        <f t="shared" si="72"/>
         <v>0.45326132192072388</v>
       </c>
       <c r="K48" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>4.14596984713992</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>13</v>
       </c>
@@ -3145,39 +3162,39 @@
         <v>419.10899999999981</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" ref="D49" si="55">C49/C53</f>
-        <v>0.25212551502343428</v>
+        <v>0.31777318102368818</v>
       </c>
       <c r="E49" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A49)*$D49</f>
-        <v>60.076766381657109</v>
+        <f t="shared" si="67"/>
+        <v>75.719370000857396</v>
       </c>
       <c r="F49" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A49)*$D49</f>
-        <v>53.75876748635455</v>
+        <f t="shared" si="68"/>
+        <v>67.756309988950889</v>
       </c>
       <c r="G49" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A49)*$D49</f>
-        <v>56.091255039997549</v>
+        <f t="shared" si="69"/>
+        <v>70.696123476492616</v>
       </c>
       <c r="H49" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A49)*$D49</f>
-        <v>73.3009566857896</v>
+        <f t="shared" si="70"/>
+        <v>92.386834295441801</v>
       </c>
       <c r="I49" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A49)*$D49</f>
-        <v>74.386070460745259</v>
+        <f t="shared" si="71"/>
+        <v>93.754486657037305</v>
       </c>
       <c r="J49" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A49)*$D49</f>
-        <v>90.459952080415505</v>
+        <f t="shared" si="72"/>
+        <v>114.01363612553139</v>
       </c>
       <c r="K49" s="16">
-        <f t="shared" si="1"/>
-        <v>827.43489364998288</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>933.75353372533493</v>
+      </c>
+      <c r="L49" s="19"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>13</v>
       </c>
@@ -3188,39 +3205,38 @@
         <v>1190.8399999999999</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" ref="D50" si="56">C50/C53</f>
-        <v>0.71637962513452735</v>
+        <v>0.6507319591342734</v>
       </c>
       <c r="E50" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A50)*$D50</f>
-        <v>170.69978568327713</v>
+        <f t="shared" si="67"/>
+        <v>155.05718206407681</v>
       </c>
       <c r="F50" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A50)*$D50</f>
-        <v>152.7480695319129</v>
+        <f t="shared" si="68"/>
+        <v>138.75052702931654</v>
       </c>
       <c r="G50" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A50)*$D50</f>
-        <v>159.3755088815337</v>
+        <f t="shared" si="69"/>
+        <v>144.77064044503865</v>
       </c>
       <c r="H50" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A50)*$D50</f>
-        <v>208.27448530025777</v>
+        <f t="shared" si="70"/>
+        <v>189.18860769060555</v>
       </c>
       <c r="I50" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A50)*$D50</f>
-        <v>211.35768534551616</v>
+        <f t="shared" si="71"/>
+        <v>191.9892691492241</v>
       </c>
       <c r="J50" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A50)*$D50</f>
-        <v>257.02938695051182</v>
+        <f t="shared" si="72"/>
+        <v>233.47570290539591</v>
       </c>
       <c r="K50" s="16">
-        <f t="shared" si="1"/>
-        <v>2351.0413013181442</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>2244.7226612427917</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>13</v>
       </c>
@@ -3231,39 +3247,39 @@
         <v>0</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" ref="D51" si="57">C51/C53</f>
+        <f t="shared" ref="D51" si="77">C51/C53</f>
         <v>0</v>
       </c>
       <c r="E51" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F51" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G51" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="H51" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="I51" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="J51" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A51)*$D51</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K51" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>13</v>
       </c>
@@ -3274,76 +3290,80 @@
         <v>0</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" ref="D52" si="58">C52/C53</f>
+        <f t="shared" ref="D52" si="78">C52/C53</f>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F52" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G52" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="H52" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="I52" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="J52" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A52)*$D52</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K52" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="19">
+        <f>1-D53</f>
+        <v>0</v>
+      </c>
       <c r="C53" s="3">
         <v>1662.3029999999997</v>
       </c>
       <c r="D53" s="5">
-        <f t="shared" ref="D53:E53" si="59">SUM(D44:D52)</f>
+        <f t="shared" ref="D53:E53" si="79">SUM(D44:D52)</f>
         <v>1</v>
       </c>
       <c r="E53" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="79"/>
         <v>238.28118457615511</v>
       </c>
       <c r="F53" s="9">
-        <f t="shared" ref="F53" si="60">SUM(F44:F52)</f>
+        <f t="shared" ref="F53" si="80">SUM(F44:F52)</f>
         <v>213.22224163372692</v>
       </c>
       <c r="G53" s="9">
-        <f t="shared" ref="G53" si="61">SUM(G44:G52)</f>
-        <v>222.4735367810118</v>
+        <f t="shared" ref="G53" si="81">SUM(G44:G52)</f>
+        <v>222.47353678101183</v>
       </c>
       <c r="H53" s="9">
-        <f t="shared" ref="H53" si="62">SUM(H44:H52)</f>
-        <v>290.73200575902251</v>
+        <f t="shared" ref="H53" si="82">SUM(H44:H52)</f>
+        <v>290.73200575902246</v>
       </c>
       <c r="I53" s="9">
-        <f t="shared" ref="I53" si="63">SUM(I44:I52)</f>
+        <f t="shared" ref="I53" si="83">SUM(I44:I52)</f>
         <v>295.03586915362894</v>
       </c>
       <c r="J53" s="9">
-        <f t="shared" ref="J53" si="64">SUM(J44:J52)</f>
-        <v>358.78935962513572</v>
+        <f t="shared" ref="J53" si="84">SUM(J44:J52)</f>
+        <v>358.78935962513566</v>
       </c>
       <c r="K53" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3281.83719752868</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
@@ -3354,39 +3374,39 @@
         <v>54.040000000000006</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" ref="D54" si="65">C54/C63</f>
+        <f t="shared" ref="D54" si="85">C54/C63</f>
         <v>2.6444152142935447E-2</v>
       </c>
       <c r="E54" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="E54:E62" si="86">SUMIFS(P:P,$M:$M,$A54)*$D54</f>
         <v>7.7463105188978343</v>
       </c>
       <c r="F54" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="F54:F62" si="87">SUMIFS(Q:Q,$M:$M,$A54)*$D54</f>
         <v>6.9316664518361613</v>
       </c>
       <c r="G54" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="G54:G62" si="88">SUMIFS(R:R,$M:$M,$A54)*$D54</f>
         <v>7.2324178730627811</v>
       </c>
       <c r="H54" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="H54:H62" si="89">SUMIFS(S:S,$M:$M,$A54)*$D54</f>
         <v>9.451440315765284</v>
       </c>
       <c r="I54" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="I54:I62" si="90">SUMIFS(T:T,$M:$M,$A54)*$D54</f>
         <v>9.5913551073794086</v>
       </c>
       <c r="J54" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A54)*$D54</f>
+        <f t="shared" ref="J54:J62" si="91">SUMIFS(U:U,$M:$M,$A54)*$D54</f>
         <v>11.663924684093296</v>
       </c>
       <c r="K54" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>106.68355910317771</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>14</v>
       </c>
@@ -3397,39 +3417,39 @@
         <v>31.033999999999992</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" ref="D55" si="66">C55/C63</f>
+        <f t="shared" ref="D55" si="92">C55/C63</f>
         <v>1.5186303064468141E-2</v>
       </c>
       <c r="E55" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="86"/>
         <v>4.4485381318185659</v>
       </c>
       <c r="F55" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="87"/>
         <v>3.9807057118113125</v>
       </c>
       <c r="G55" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="88"/>
         <v>4.1534207304335728</v>
       </c>
       <c r="H55" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="89"/>
         <v>5.4277571939204234</v>
       </c>
       <c r="I55" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="90"/>
         <v>5.5081072243229539</v>
       </c>
       <c r="J55" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A55)*$D55</f>
+        <f t="shared" si="91"/>
         <v>6.6983389830893998</v>
       </c>
       <c r="K55" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>61.266054278460686</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>14</v>
       </c>
@@ -3440,39 +3460,39 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" ref="D56" si="67">C56/C63</f>
+        <f t="shared" ref="D56" si="93">C56/C63</f>
         <v>9.933684095144143E-5</v>
       </c>
       <c r="E56" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="86"/>
         <v>2.9098834850782015E-2</v>
       </c>
       <c r="F56" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="87"/>
         <v>2.6038643407156559E-2</v>
       </c>
       <c r="G56" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="88"/>
         <v>2.716840910865552E-2</v>
       </c>
       <c r="H56" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="89"/>
         <v>3.5504115175802223E-2</v>
       </c>
       <c r="I56" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="90"/>
         <v>3.6029701828238704E-2</v>
       </c>
       <c r="J56" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A56)*$D56</f>
+        <f t="shared" si="91"/>
         <v>4.3815261119003301E-2</v>
       </c>
       <c r="K56" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>0.40075430233058984</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>14</v>
       </c>
@@ -3483,39 +3503,39 @@
         <v>0</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" ref="D57" si="68">C57/C63</f>
+        <f t="shared" ref="D57" si="94">C57/C63</f>
         <v>0</v>
       </c>
       <c r="E57" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="F57" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="G57" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="H57" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="I57" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="J57" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A57)*$D57</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="K57" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>14</v>
       </c>
@@ -3526,39 +3546,39 @@
         <v>1.6250000000000002</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" ref="D58" si="69">C58/C63</f>
+        <f t="shared" ref="D58" si="95">C58/C63</f>
         <v>7.9518407165562728E-4</v>
       </c>
       <c r="E58" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="86"/>
         <v>0.2329340228202994</v>
       </c>
       <c r="F58" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="87"/>
         <v>0.20843741643659808</v>
       </c>
       <c r="G58" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="88"/>
         <v>0.21748110739687304</v>
       </c>
       <c r="H58" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="89"/>
         <v>0.28420781852551047</v>
       </c>
       <c r="I58" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="90"/>
         <v>0.28841510084181232</v>
       </c>
       <c r="J58" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A58)*$D58</f>
+        <f t="shared" si="91"/>
         <v>0.3507379276767506</v>
       </c>
       <c r="K58" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.2080085777694998</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>14</v>
       </c>
@@ -3569,39 +3589,39 @@
         <v>610.19999999999936</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" ref="D59" si="70">C59/C63</f>
-        <v>0.29859773570723891</v>
+        <v>0.36107737928507372</v>
       </c>
       <c r="E59" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A59)*$D59</f>
-        <v>87.468517369197869</v>
+        <f t="shared" si="86"/>
+        <v>105.77073850481732</v>
       </c>
       <c r="F59" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A59)*$D59</f>
-        <v>78.269853236684312</v>
+        <f t="shared" si="87"/>
+        <v>94.647313439236413</v>
       </c>
       <c r="G59" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A59)*$D59</f>
-        <v>81.665828759121098</v>
+        <f t="shared" si="88"/>
+        <v>98.753874859916351</v>
       </c>
       <c r="H59" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A59)*$D59</f>
-        <v>106.72222207031771</v>
+        <f t="shared" si="89"/>
+        <v>129.05315629858532</v>
       </c>
       <c r="I59" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A59)*$D59</f>
-        <v>108.30208894379918</v>
+        <f t="shared" si="90"/>
+        <v>130.96360008994515</v>
       </c>
       <c r="J59" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A59)*$D59</f>
-        <v>131.70478982667876</v>
+        <f t="shared" si="91"/>
+        <v>159.26316466289168</v>
       </c>
       <c r="K59" s="16">
-        <f t="shared" si="1"/>
-        <v>1204.6318979415055</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>1329.0129252346769</v>
+      </c>
+      <c r="L59" s="19"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>14</v>
       </c>
@@ -3612,39 +3632,38 @@
         <v>1346.4500000000003</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" ref="D60" si="71">C60/C63</f>
-        <v>0.65887728817275037</v>
+        <v>0.59639764459491562</v>
       </c>
       <c r="E60" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A60)*$D60</f>
-        <v>193.00554770854902</v>
+        <f t="shared" si="86"/>
+        <v>174.7033265729296</v>
       </c>
       <c r="F60" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A60)*$D60</f>
-        <v>172.70803652988153</v>
+        <f t="shared" si="87"/>
+        <v>156.33057632732945</v>
       </c>
       <c r="G60" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A60)*$D60</f>
-        <v>180.20149972585827</v>
+        <f t="shared" si="88"/>
+        <v>163.11345362506302</v>
       </c>
       <c r="H60" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A60)*$D60</f>
-        <v>235.49022600226064</v>
+        <f t="shared" si="89"/>
+        <v>213.15929177399306</v>
       </c>
       <c r="I60" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A60)*$D60</f>
-        <v>238.97631540212811</v>
+        <f t="shared" si="90"/>
+        <v>216.31480425598218</v>
       </c>
       <c r="J60" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A60)*$D60</f>
-        <v>290.61605090483744</v>
+        <f t="shared" si="91"/>
+        <v>263.05767606862452</v>
       </c>
       <c r="K60" s="16">
-        <f t="shared" si="1"/>
-        <v>2658.1065535616876</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>2533.7255262685171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>14</v>
       </c>
@@ -3655,39 +3674,39 @@
         <v>0</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" ref="D61" si="72">C61/C63</f>
+        <f t="shared" ref="D61" si="96">C61/C63</f>
         <v>0</v>
       </c>
       <c r="E61" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="F61" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="G61" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="H61" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="I61" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="J61" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A61)*$D61</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="K61" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>14</v>
       </c>
@@ -3698,76 +3717,80 @@
         <v>0</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" ref="D62" si="73">C62/C63</f>
+        <f t="shared" ref="D62" si="97">C62/C63</f>
         <v>0</v>
       </c>
       <c r="E62" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="F62" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="G62" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="H62" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="I62" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="J62" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A62)*$D62</f>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="K62" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="19">
+        <f>1-D63</f>
+        <v>0</v>
+      </c>
       <c r="C63" s="3">
         <v>2043.5519999999997</v>
       </c>
       <c r="D63" s="5">
-        <f t="shared" ref="D63:E63" si="74">SUM(D54:D62)</f>
+        <f t="shared" ref="D63:E63" si="98">SUM(D54:D62)</f>
         <v>1</v>
       </c>
       <c r="E63" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="98"/>
         <v>292.93094658613438</v>
       </c>
       <c r="F63" s="9">
-        <f t="shared" ref="F63" si="75">SUM(F54:F62)</f>
-        <v>262.12473799005704</v>
+        <f t="shared" ref="F63" si="99">SUM(F54:F62)</f>
+        <v>262.1247379900571</v>
       </c>
       <c r="G63" s="9">
-        <f t="shared" ref="G63" si="76">SUM(G54:G62)</f>
+        <f t="shared" ref="G63" si="100">SUM(G54:G62)</f>
         <v>273.49781660498127</v>
       </c>
       <c r="H63" s="9">
-        <f t="shared" ref="H63" si="77">SUM(H54:H62)</f>
+        <f t="shared" ref="H63" si="101">SUM(H54:H62)</f>
         <v>357.41135751596539</v>
       </c>
       <c r="I63" s="9">
-        <f t="shared" ref="I63" si="78">SUM(I54:I62)</f>
+        <f t="shared" ref="I63" si="102">SUM(I54:I62)</f>
         <v>362.70231148029973</v>
       </c>
       <c r="J63" s="9">
-        <f t="shared" ref="J63" si="79">SUM(J54:J62)</f>
+        <f t="shared" ref="J63" si="103">SUM(J54:J62)</f>
         <v>441.07765758749463</v>
       </c>
       <c r="K63" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>4034.296827764932</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>15</v>
       </c>
@@ -3778,39 +3801,39 @@
         <v>134.64500000000001</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" ref="D64" si="80">C64/C73</f>
+        <f t="shared" ref="D64" si="104">C64/C73</f>
         <v>3.4014432052328951E-2</v>
       </c>
       <c r="E64" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="E64:E72" si="105">SUMIFS(P:P,$M:$M,$A64)*$D64</f>
         <v>19.300554770854905</v>
       </c>
       <c r="F64" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="F64:F72" si="106">SUMIFS(Q:Q,$M:$M,$A64)*$D64</f>
         <v>17.270803652988157</v>
       </c>
       <c r="G64" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="G64:G72" si="107">SUMIFS(R:R,$M:$M,$A64)*$D64</f>
         <v>18.020149972585831</v>
       </c>
       <c r="H64" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="H64:H72" si="108">SUMIFS(S:S,$M:$M,$A64)*$D64</f>
         <v>23.549022600226071</v>
       </c>
       <c r="I64" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="I64:I72" si="109">SUMIFS(T:T,$M:$M,$A64)*$D64</f>
         <v>23.89763154021281</v>
       </c>
       <c r="J64" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A64)*$D64</f>
+        <f t="shared" ref="J64:J72" si="110">SUMIFS(U:U,$M:$M,$A64)*$D64</f>
         <v>29.061605090483749</v>
       </c>
       <c r="K64" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>265.77878205940385</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>15</v>
       </c>
@@ -3821,39 +3844,39 @@
         <v>69.476800000000125</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" ref="D65" si="81">C65/C73</f>
+        <f t="shared" ref="D65" si="111">C65/C73</f>
         <v>1.7551441886540547E-2</v>
       </c>
       <c r="E65" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="105"/>
         <v>9.9590833948808655</v>
       </c>
       <c r="F65" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="106"/>
         <v>8.9117321195583159</v>
       </c>
       <c r="G65" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="107"/>
         <v>9.29839470916375</v>
       </c>
       <c r="H65" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="108"/>
         <v>12.15129216377429</v>
       </c>
       <c r="I65" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="109"/>
         <v>12.331174325025513</v>
       </c>
       <c r="J65" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A65)*$D65</f>
+        <f t="shared" si="110"/>
         <v>14.995783909915145</v>
       </c>
       <c r="K65" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>137.14181206420454</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>15</v>
       </c>
@@ -3864,39 +3887,39 @@
         <v>0.68300000000000027</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" ref="D66" si="82">C66/C73</f>
+        <f t="shared" ref="D66" si="112">C66/C73</f>
         <v>1.7254155068320903E-4</v>
       </c>
       <c r="E66" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="105"/>
         <v>9.790396159154742E-2</v>
       </c>
       <c r="F66" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="106"/>
         <v>8.7607849493044038E-2</v>
       </c>
       <c r="G66" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="107"/>
         <v>9.140898237050113E-2</v>
       </c>
       <c r="H66" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="108"/>
         <v>0.11945473234026076</v>
       </c>
       <c r="I66" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="109"/>
         <v>0.12122308546151253</v>
       </c>
       <c r="J66" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A66)*$D66</f>
+        <f t="shared" si="110"/>
         <v>0.14741784898659741</v>
       </c>
       <c r="K66" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>1.3481890017941469</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>15</v>
       </c>
@@ -3907,39 +3930,39 @@
         <v>0</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" ref="D67" si="83">C67/C73</f>
+        <f t="shared" ref="D67" si="113">C67/C73</f>
         <v>0</v>
       </c>
       <c r="E67" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="F67" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="G67" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="H67" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="I67" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="J67" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A67)*$D67</f>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="K67" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>15</v>
       </c>
@@ -3950,39 +3973,39 @@
         <v>3.975000000000001</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" ref="D68" si="84">C68/C73</f>
+        <f t="shared" ref="D68" si="114">C68/C73</f>
         <v>1.0041766675926145E-3</v>
       </c>
       <c r="E68" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="105"/>
         <v>0.56979245582196325</v>
       </c>
       <c r="F68" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="106"/>
         <v>0.50986998789875537</v>
       </c>
       <c r="G68" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="107"/>
         <v>0.53199224732465877</v>
       </c>
       <c r="H68" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="108"/>
         <v>0.69521604839317186</v>
       </c>
       <c r="I68" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="109"/>
         <v>0.70550770821304853</v>
       </c>
       <c r="J68" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A68)*$D68</f>
+        <f t="shared" si="110"/>
         <v>0.85795893077851315</v>
       </c>
       <c r="K68" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>7.8463415550977045</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>15</v>
       </c>
@@ -3993,39 +4016,39 @@
         <v>927.41999999999985</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" ref="D69" si="85">C69/C73</f>
-        <v>0.23428767926006094</v>
+        <v>0.38371283734012818</v>
       </c>
       <c r="E69" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A69)*$D69</f>
-        <v>132.94010550400125</v>
+        <f t="shared" si="105"/>
+        <v>217.72730533821178</v>
       </c>
       <c r="F69" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A69)*$D69</f>
-        <v>118.95940230869525</v>
+        <f t="shared" si="106"/>
+        <v>194.82991991861252</v>
       </c>
       <c r="G69" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A69)*$D69</f>
-        <v>124.12081761354335</v>
+        <f t="shared" si="107"/>
+        <v>203.28320827576792</v>
       </c>
       <c r="H69" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A69)*$D69</f>
-        <v>162.2030861888793</v>
+        <f t="shared" si="108"/>
+        <v>265.65377498051902</v>
       </c>
       <c r="I69" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A69)*$D69</f>
-        <v>164.60426635243908</v>
+        <f t="shared" si="109"/>
+        <v>269.5863917379782</v>
       </c>
       <c r="J69" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A69)*$D69</f>
-        <v>200.17315008367507</v>
+        <f t="shared" si="110"/>
+        <v>327.84057454707101</v>
       </c>
       <c r="K69" s="16">
-        <f t="shared" ref="K69:K132" si="86">SUM(C69:J69)</f>
-        <v>1830.655115730493</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K69:K132" si="115">SUM(C69:J69)</f>
+        <v>2406.7248876355006</v>
+      </c>
+      <c r="L69" s="19"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>15</v>
       </c>
@@ -4036,39 +4059,38 @@
         <v>2822.2370000000001</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" ref="D70" si="87">C70/C73</f>
-        <v>0.71296214989096285</v>
+        <v>0.56353699181089567</v>
       </c>
       <c r="E70" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A70)*$D70</f>
-        <v>404.5507801614113</v>
+        <f t="shared" si="105"/>
+        <v>319.76358032720083</v>
       </c>
       <c r="F70" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A70)*$D70</f>
-        <v>362.00602390878481</v>
+        <f t="shared" si="106"/>
+        <v>286.1355062988676</v>
       </c>
       <c r="G70" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A70)*$D70</f>
-        <v>377.7127557516485</v>
+        <f t="shared" si="107"/>
+        <v>298.55036508942396</v>
       </c>
       <c r="H70" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A70)*$D70</f>
-        <v>493.6011206966038</v>
+        <f t="shared" si="108"/>
+        <v>390.15043190496414</v>
       </c>
       <c r="I70" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A70)*$D70</f>
-        <v>500.90816551045771</v>
+        <f t="shared" si="109"/>
+        <v>395.92604012491859</v>
       </c>
       <c r="J70" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A70)*$D70</f>
-        <v>609.14803494932289</v>
+        <f t="shared" si="110"/>
+        <v>481.48061048592695</v>
       </c>
       <c r="K70" s="16">
-        <f t="shared" si="86"/>
-        <v>5570.8768431281205</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>4994.8070712231138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>15</v>
       </c>
@@ -4079,39 +4101,39 @@
         <v>0</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" ref="D71" si="88">C71/C73</f>
+        <f t="shared" ref="D71" si="116">C71/C73</f>
         <v>0</v>
       </c>
       <c r="E71" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="F71" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="G71" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="H71" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="I71" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="J71" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A71)*$D71</f>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="K71" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>15</v>
       </c>
@@ -4122,76 +4144,80 @@
         <v>0.03</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" ref="D72" si="89">C72/C73</f>
+        <f t="shared" ref="D72" si="117">C72/C73</f>
         <v>7.5786918308876551E-6</v>
       </c>
       <c r="E72" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="105"/>
         <v>4.300320421297835E-3</v>
       </c>
       <c r="F72" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="106"/>
         <v>3.8480753803679644E-3</v>
       </c>
       <c r="G72" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="107"/>
         <v>4.015035828865348E-3</v>
       </c>
       <c r="H72" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="108"/>
         <v>5.246913572778655E-3</v>
       </c>
       <c r="I72" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="109"/>
         <v>5.3245864770796111E-3</v>
       </c>
       <c r="J72" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A72)*$D72</f>
+        <f t="shared" si="110"/>
         <v>6.4751617417246263E-3</v>
       </c>
       <c r="K72" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>5.9217672113944929E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B73" s="19">
+        <f>1-D73</f>
+        <v>0</v>
+      </c>
       <c r="C73" s="3">
         <v>3958.4668000000001</v>
       </c>
       <c r="D73" s="5">
-        <f t="shared" ref="D73:E73" si="90">SUM(D64:D72)</f>
-        <v>1</v>
+        <f t="shared" ref="D73:E73" si="118">SUM(D64:D72)</f>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E73" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="118"/>
         <v>567.42252056898315</v>
       </c>
       <c r="F73" s="9">
-        <f t="shared" ref="F73" si="91">SUM(F64:F72)</f>
-        <v>507.74928790279864</v>
+        <f t="shared" ref="F73" si="119">SUM(F64:F72)</f>
+        <v>507.74928790279876</v>
       </c>
       <c r="G73" s="9">
-        <f t="shared" ref="G73" si="92">SUM(G64:G72)</f>
+        <f t="shared" ref="G73" si="120">SUM(G64:G72)</f>
         <v>529.77953431246544</v>
       </c>
       <c r="H73" s="9">
-        <f t="shared" ref="H73" si="93">SUM(H64:H72)</f>
-        <v>692.32443934378966</v>
+        <f t="shared" ref="H73" si="121">SUM(H64:H72)</f>
+        <v>692.32443934378978</v>
       </c>
       <c r="I73" s="9">
-        <f t="shared" ref="I73" si="94">SUM(I64:I72)</f>
+        <f t="shared" ref="I73" si="122">SUM(I64:I72)</f>
         <v>702.57329310828675</v>
       </c>
       <c r="J73" s="9">
-        <f t="shared" ref="J73" si="95">SUM(J64:J72)</f>
+        <f t="shared" ref="J73" si="123">SUM(J64:J72)</f>
         <v>854.39042597490368</v>
       </c>
       <c r="K73" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>7813.7063012112276</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>16</v>
       </c>
@@ -4202,39 +4228,39 @@
         <v>24.514999999999997</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" ref="D74" si="96">C74/C83</f>
+        <f t="shared" ref="D74" si="124">C74/C83</f>
         <v>2.0051217918255811E-2</v>
       </c>
       <c r="E74" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="E74:E82" si="125">SUMIFS(P:P,$M:$M,$A74)*$D74</f>
         <v>3.5140785042705467</v>
       </c>
       <c r="F74" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="F74:F82" si="126">SUMIFS(Q:Q,$M:$M,$A74)*$D74</f>
         <v>3.1445189316573545</v>
       </c>
       <c r="G74" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="G74:G82" si="127">SUMIFS(R:R,$M:$M,$A74)*$D74</f>
         <v>3.2809534448211335</v>
       </c>
       <c r="H74" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="H74:H82" si="128">SUMIFS(S:S,$M:$M,$A74)*$D74</f>
         <v>4.2876028745556232</v>
       </c>
       <c r="I74" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="I74:I82" si="129">SUMIFS(T:T,$M:$M,$A74)*$D74</f>
         <v>4.3510745828535553</v>
       </c>
       <c r="J74" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A74)*$D74</f>
+        <f t="shared" ref="J74:J82" si="130">SUMIFS(U:U,$M:$M,$A74)*$D74</f>
         <v>5.2912863366126395</v>
       </c>
       <c r="K74" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>48.404565892689106</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>16</v>
       </c>
@@ -4245,39 +4271,39 @@
         <v>18.602999999999966</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" ref="D75" si="97">C75/C83</f>
+        <f t="shared" ref="D75" si="131">C75/C83</f>
         <v>1.5215696795158567E-2</v>
       </c>
       <c r="E75" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="125"/>
         <v>2.6666286932467829</v>
       </c>
       <c r="F75" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="126"/>
         <v>2.3861915433661705</v>
       </c>
       <c r="G75" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="127"/>
         <v>2.4897237174793982</v>
       </c>
       <c r="H75" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="128"/>
         <v>3.2536111064800379</v>
       </c>
       <c r="I75" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="129"/>
         <v>3.3017760744370612</v>
       </c>
       <c r="J75" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A75)*$D75</f>
+        <f t="shared" si="130"/>
         <v>4.0152477960434334</v>
       </c>
       <c r="K75" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>36.731394627848012</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>16</v>
       </c>
@@ -4288,39 +4314,39 @@
         <v>0.32000000000000006</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" ref="D76" si="98">C76/C83</f>
+        <f t="shared" ref="D76" si="132">C76/C83</f>
         <v>2.6173321369944372E-4</v>
       </c>
       <c r="E76" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="125"/>
         <v>4.5870084493843589E-2</v>
       </c>
       <c r="F76" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="126"/>
         <v>4.1046137390591639E-2</v>
       </c>
       <c r="G76" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="127"/>
         <v>4.2827048841230397E-2</v>
       </c>
       <c r="H76" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="128"/>
         <v>5.5967078109639003E-2</v>
       </c>
       <c r="I76" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="129"/>
         <v>5.6795589088849206E-2</v>
       </c>
       <c r="J76" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A76)*$D76</f>
+        <f t="shared" si="130"/>
         <v>6.9068391911729365E-2</v>
       </c>
       <c r="K76" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.63183606304958273</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>16</v>
       </c>
@@ -4331,39 +4357,39 @@
         <v>0</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" ref="D77" si="99">C77/C83</f>
+        <f t="shared" ref="D77" si="133">C77/C83</f>
         <v>0</v>
       </c>
       <c r="E77" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="F77" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="G77" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="H77" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="I77" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="J77" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A77)*$D77</f>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="K77" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>16</v>
       </c>
@@ -4374,39 +4400,39 @@
         <v>0.8</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" ref="D78" si="100">C78/C83</f>
+        <f t="shared" ref="D78" si="134">C78/C83</f>
         <v>6.5433303424860915E-4</v>
       </c>
       <c r="E78" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="125"/>
         <v>0.11467521123460894</v>
       </c>
       <c r="F78" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="126"/>
         <v>0.10261534347647906</v>
       </c>
       <c r="G78" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="127"/>
         <v>0.10706762210307597</v>
       </c>
       <c r="H78" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="128"/>
         <v>0.13991769527409748</v>
       </c>
       <c r="I78" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="129"/>
         <v>0.14198897272212299</v>
       </c>
       <c r="J78" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A78)*$D78</f>
+        <f t="shared" si="130"/>
         <v>0.17267097977932336</v>
       </c>
       <c r="K78" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>1.5795901576239566</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>16</v>
       </c>
@@ -4417,39 +4443,39 @@
         <v>309.83799999999997</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79" si="101">C79/C83</f>
-        <v>0.25342154833190067</v>
+        <v>0.30709732985357951</v>
       </c>
       <c r="E79" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A79)*$D79</f>
-        <v>44.413422623135951</v>
+        <f t="shared" si="125"/>
+        <v>53.820377892098556</v>
       </c>
       <c r="F79" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A79)*$D79</f>
-        <v>39.742665990081647</v>
+        <f t="shared" si="126"/>
+        <v>48.160334774816747</v>
       </c>
       <c r="G79" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A79)*$D79</f>
-        <v>41.467022371466058</v>
+        <f t="shared" si="127"/>
+        <v>50.249917306076483</v>
       </c>
       <c r="H79" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A79)*$D79</f>
-        <v>54.189773585419758</v>
+        <f t="shared" si="128"/>
+        <v>65.66740233019722</v>
       </c>
       <c r="I79" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A79)*$D79</f>
-        <v>54.991974162846418</v>
+        <f t="shared" si="129"/>
+        <v>66.639512464305014</v>
       </c>
       <c r="J79" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A79)*$D79</f>
-        <v>66.875038791082488</v>
+        <f t="shared" si="130"/>
+        <v>81.039461647116653</v>
       </c>
       <c r="K79" s="16">
-        <f t="shared" si="86"/>
-        <v>611.77131907236412</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>675.72210374446433</v>
+      </c>
+      <c r="L79" s="19"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>16</v>
       </c>
@@ -4460,39 +4486,38 @@
         <v>868.50299999999993</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" ref="D80" si="102">C80/C83</f>
-        <v>0.71036275405502458</v>
+        <v>0.65668697253334563</v>
       </c>
       <c r="E80" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A80)*$D80</f>
-        <v>124.49470622861443</v>
+        <f t="shared" si="125"/>
+        <v>115.08775095965181</v>
       </c>
       <c r="F80" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A80)*$D80</f>
-        <v>111.4021670691906</v>
+        <f t="shared" si="126"/>
+        <v>102.98449828445548</v>
       </c>
       <c r="G80" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A80)*$D80</f>
-        <v>116.23568874923471</v>
+        <f t="shared" si="127"/>
+        <v>107.45279381462427</v>
       </c>
       <c r="H80" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A80)*$D80</f>
-        <v>151.89867262329932</v>
+        <f t="shared" si="128"/>
+        <v>140.42104387852183</v>
       </c>
       <c r="I80" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A80)*$D80</f>
-        <v>154.14731097010244</v>
+        <f t="shared" si="129"/>
+        <v>142.49977266864383</v>
       </c>
       <c r="J80" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A80)*$D80</f>
-        <v>187.45657993910206</v>
+        <f t="shared" si="130"/>
+        <v>173.29215708306788</v>
       </c>
       <c r="K80" s="16">
-        <f t="shared" si="86"/>
-        <v>1714.8484883335984</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>1650.8977036614983</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>16</v>
       </c>
@@ -4503,39 +4528,39 @@
         <v>0</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" ref="D81" si="103">C81/C83</f>
+        <f t="shared" ref="D81" si="135">C81/C83</f>
         <v>0</v>
       </c>
       <c r="E81" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="F81" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="G81" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="H81" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="I81" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="J81" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A81)*$D81</f>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="K81" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>16</v>
       </c>
@@ -4546,76 +4571,80 @@
         <v>0.04</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" ref="D82" si="104">C82/C83</f>
+        <f t="shared" ref="D82" si="136">C82/C83</f>
         <v>3.2716651712430458E-5</v>
       </c>
       <c r="E82" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="125"/>
         <v>5.733760561730447E-3</v>
       </c>
       <c r="F82" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="126"/>
         <v>5.1307671738239531E-3</v>
       </c>
       <c r="G82" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="127"/>
         <v>5.3533811051537988E-3</v>
       </c>
       <c r="H82" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="128"/>
         <v>6.9958847637048736E-3</v>
       </c>
       <c r="I82" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="129"/>
         <v>7.0994486361061499E-3</v>
       </c>
       <c r="J82" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A82)*$D82</f>
+        <f t="shared" si="130"/>
         <v>8.6335489889661689E-3</v>
       </c>
       <c r="K82" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>7.8979507881197814E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B83" s="19">
+        <f>1-D83</f>
+        <v>0</v>
+      </c>
       <c r="C83" s="3">
         <v>1222.6189999999997</v>
       </c>
       <c r="D83" s="5">
-        <f t="shared" ref="D83:E83" si="105">SUM(D74:D82)</f>
+        <f t="shared" ref="D83:E83" si="137">SUM(D74:D82)</f>
         <v>1</v>
       </c>
       <c r="E83" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="137"/>
         <v>175.25511510555788</v>
       </c>
       <c r="F83" s="9">
-        <f t="shared" ref="F83" si="106">SUM(F74:F82)</f>
-        <v>156.82433578233668</v>
+        <f t="shared" ref="F83" si="138">SUM(F74:F82)</f>
+        <v>156.82433578233665</v>
       </c>
       <c r="G83" s="9">
-        <f t="shared" ref="G83" si="107">SUM(G74:G82)</f>
+        <f t="shared" ref="G83" si="139">SUM(G74:G82)</f>
         <v>163.62863633505074</v>
       </c>
       <c r="H83" s="9">
-        <f t="shared" ref="H83" si="108">SUM(H74:H82)</f>
-        <v>213.83254084790218</v>
+        <f t="shared" ref="H83" si="140">SUM(H74:H82)</f>
+        <v>213.83254084790215</v>
       </c>
       <c r="I83" s="9">
-        <f t="shared" ref="I83" si="109">SUM(I74:I82)</f>
+        <f t="shared" ref="I83" si="141">SUM(I74:I82)</f>
         <v>216.99801980068654</v>
       </c>
       <c r="J83" s="9">
-        <f t="shared" ref="J83" si="110">SUM(J74:J82)</f>
+        <f t="shared" ref="J83" si="142">SUM(J74:J82)</f>
         <v>263.88852578352061</v>
       </c>
       <c r="K83" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>2414.0461736550542</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>17</v>
       </c>
@@ -4626,39 +4655,39 @@
         <v>10.979999999999997</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" ref="D84" si="111">C84/C93</f>
+        <f t="shared" ref="D84" si="143">C84/C93</f>
         <v>1.4896821197443932E-2</v>
       </c>
       <c r="E84" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="E84:E92" si="144">SUMIFS(P:P,$M:$M,$A84)*$D84</f>
         <v>1.5739172741950069</v>
       </c>
       <c r="F84" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="F84:F92" si="145">SUMIFS(Q:Q,$M:$M,$A84)*$D84</f>
         <v>1.4083955892146744</v>
       </c>
       <c r="G84" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="G84:G92" si="146">SUMIFS(R:R,$M:$M,$A84)*$D84</f>
         <v>1.469503113364717</v>
       </c>
       <c r="H84" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="H84:H92" si="147">SUMIFS(S:S,$M:$M,$A84)*$D84</f>
         <v>1.920370367636987</v>
       </c>
       <c r="I84" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="I84:I92" si="148">SUMIFS(T:T,$M:$M,$A84)*$D84</f>
         <v>1.9487986506111372</v>
       </c>
       <c r="J84" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A84)*$D84</f>
+        <f t="shared" ref="J84:J92" si="149">SUMIFS(U:U,$M:$M,$A84)*$D84</f>
         <v>2.3699091974712125</v>
       </c>
       <c r="K84" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>21.685791013691176</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>17</v>
       </c>
@@ -4669,39 +4698,39 @@
         <v>11.515999999999977</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" ref="D85" si="112">C85/C93</f>
+        <f t="shared" ref="D85" si="150">C85/C93</f>
         <v>1.5624024855169767E-2</v>
       </c>
       <c r="E85" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="144"/>
         <v>1.6507496657221921</v>
       </c>
       <c r="F85" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="145"/>
         <v>1.4771478693439131</v>
       </c>
       <c r="G85" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="146"/>
         <v>1.5412384201737754</v>
       </c>
       <c r="H85" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="147"/>
         <v>2.014115223470629</v>
       </c>
       <c r="I85" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="148"/>
         <v>2.0439312623349561</v>
       </c>
       <c r="J85" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A85)*$D85</f>
+        <f t="shared" si="149"/>
         <v>2.4855987539233548</v>
       </c>
       <c r="K85" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>22.744405219823967</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>17</v>
       </c>
@@ -4712,39 +4741,39 @@
         <v>4.4000000000000004E-2</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" ref="D86" si="113">C86/C93</f>
+        <f t="shared" ref="D86" si="151">C86/C93</f>
         <v>5.969582264913782E-5</v>
       </c>
       <c r="E86" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="144"/>
         <v>6.307136617903491E-3</v>
       </c>
       <c r="F86" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="145"/>
         <v>5.6438438912063483E-3</v>
       </c>
       <c r="G86" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="146"/>
         <v>5.8887192156691784E-3</v>
       </c>
       <c r="H86" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="147"/>
         <v>7.6954732400753602E-3</v>
       </c>
       <c r="I86" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="148"/>
         <v>7.809393499716764E-3</v>
       </c>
       <c r="J86" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A86)*$D86</f>
+        <f t="shared" si="149"/>
         <v>9.496903887862786E-3</v>
       </c>
       <c r="K86" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>8.6901166175083061E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>17</v>
       </c>
@@ -4755,39 +4784,39 @@
         <v>0</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" ref="D87" si="114">C87/C93</f>
+        <f t="shared" ref="D87" si="152">C87/C93</f>
         <v>0</v>
       </c>
       <c r="E87" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="F87" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="G87" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="H87" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I87" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="J87" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A87)*$D87</f>
+        <f t="shared" si="149"/>
         <v>0</v>
       </c>
       <c r="K87" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>17</v>
       </c>
@@ -4798,39 +4827,39 @@
         <v>0.2</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" ref="D88" si="115">C88/C93</f>
+        <f t="shared" ref="D88" si="153">C88/C93</f>
         <v>2.7134464840517192E-4</v>
       </c>
       <c r="E88" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="144"/>
         <v>2.8668802808652232E-2</v>
       </c>
       <c r="F88" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="145"/>
         <v>2.5653835869119766E-2</v>
       </c>
       <c r="G88" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="146"/>
         <v>2.6766905525768991E-2</v>
       </c>
       <c r="H88" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="147"/>
         <v>3.4979423818524369E-2</v>
       </c>
       <c r="I88" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="148"/>
         <v>3.5497243180530748E-2</v>
       </c>
       <c r="J88" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A88)*$D88</f>
+        <f t="shared" si="149"/>
         <v>4.3167744944830846E-2</v>
       </c>
       <c r="K88" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.39500530079583213</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>17</v>
       </c>
@@ -4841,39 +4870,39 @@
         <v>277.15499999999992</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" ref="D89" si="116">C89/C93</f>
         <v>0.37602263014367698</v>
       </c>
       <c r="E89" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="144"/>
         <v>39.728510212160032</v>
       </c>
       <c r="F89" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="145"/>
         <v>35.550444401529433</v>
       </c>
       <c r="G89" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="146"/>
         <v>37.092908504972513</v>
       </c>
       <c r="H89" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="147"/>
         <v>48.473611042115586</v>
       </c>
       <c r="I89" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="148"/>
         <v>49.191192168499974</v>
       </c>
       <c r="J89" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A89)*$D89</f>
+        <f t="shared" si="149"/>
         <v>59.82078175092294</v>
       </c>
       <c r="K89" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>547.388470710344</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L89" s="19"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>17</v>
       </c>
@@ -4884,39 +4913,39 @@
         <v>437.05499999999995</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" ref="D90" si="117">C90/C93</f>
+        <f t="shared" ref="D90" si="154">C90/C93</f>
         <v>0.5929626765436119</v>
       </c>
       <c r="E90" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="144"/>
         <v>62.649218057677487</v>
       </c>
       <c r="F90" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="145"/>
         <v>56.060686178890684</v>
       </c>
       <c r="G90" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="146"/>
         <v>58.493049472824815</v>
       </c>
       <c r="H90" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="147"/>
         <v>76.439660385025817</v>
       </c>
       <c r="I90" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="148"/>
         <v>77.571238091334308</v>
       </c>
       <c r="J90" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A90)*$D90</f>
+        <f t="shared" si="149"/>
         <v>94.333393834315203</v>
       </c>
       <c r="K90" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>863.19520869661187</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>17</v>
       </c>
@@ -4927,39 +4956,39 @@
         <v>0</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" ref="D91" si="118">C91/C93</f>
+        <f t="shared" ref="D91" si="155">C91/C93</f>
         <v>0</v>
       </c>
       <c r="E91" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="F91" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="G91" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="H91" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I91" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="J91" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A91)*$D91</f>
+        <f t="shared" si="149"/>
         <v>0</v>
       </c>
       <c r="K91" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>17</v>
       </c>
@@ -4970,76 +4999,80 @@
         <v>0.12</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" ref="D92" si="119">C92/C93</f>
+        <f t="shared" ref="D92" si="156">C92/C93</f>
         <v>1.6280678904310314E-4</v>
       </c>
       <c r="E92" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="144"/>
         <v>1.7201281685191337E-2</v>
       </c>
       <c r="F92" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="145"/>
         <v>1.5392301521471858E-2</v>
       </c>
       <c r="G92" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="146"/>
         <v>1.6060143315461396E-2</v>
       </c>
       <c r="H92" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="147"/>
         <v>2.098765429111462E-2</v>
       </c>
       <c r="I92" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="148"/>
         <v>2.1298345908318445E-2</v>
       </c>
       <c r="J92" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A92)*$D92</f>
+        <f t="shared" si="149"/>
         <v>2.5900646966898505E-2</v>
       </c>
       <c r="K92" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.23700318047749927</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B93" s="19">
+        <f>1-D93</f>
+        <v>0</v>
+      </c>
       <c r="C93" s="3">
         <v>737.06999999999982</v>
       </c>
       <c r="D93" s="5">
-        <f t="shared" ref="D93:E93" si="120">SUM(D84:D92)</f>
+        <f t="shared" ref="D93:E93" si="157">SUM(D84:D92)</f>
         <v>1</v>
       </c>
       <c r="E93" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="157"/>
         <v>105.65457243086647</v>
       </c>
       <c r="F93" s="9">
-        <f t="shared" ref="F93" si="121">SUM(F84:F92)</f>
+        <f t="shared" ref="F93" si="158">SUM(F84:F92)</f>
         <v>94.543364020260498</v>
       </c>
       <c r="G93" s="9">
-        <f t="shared" ref="G93" si="122">SUM(G84:G92)</f>
+        <f t="shared" ref="G93" si="159">SUM(G84:G92)</f>
         <v>98.645415279392722</v>
       </c>
       <c r="H93" s="9">
-        <f t="shared" ref="H93" si="123">SUM(H84:H92)</f>
+        <f t="shared" ref="H93" si="160">SUM(H84:H92)</f>
         <v>128.91141956959871</v>
       </c>
       <c r="I93" s="9">
-        <f t="shared" ref="I93" si="124">SUM(I84:I92)</f>
+        <f t="shared" ref="I93" si="161">SUM(I84:I92)</f>
         <v>130.81976515536894</v>
       </c>
       <c r="J93" s="9">
-        <f t="shared" ref="J93" si="125">SUM(J84:J92)</f>
+        <f t="shared" ref="J93" si="162">SUM(J84:J92)</f>
         <v>159.0882488324323</v>
       </c>
       <c r="K93" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>1455.7327852879196</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>18</v>
       </c>
@@ -5050,39 +5083,39 @@
         <v>13.49499999999999</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D94" si="126">C94/C103</f>
+        <f t="shared" ref="D94" si="163">C94/C103</f>
         <v>1.2020247815735253E-2</v>
       </c>
       <c r="E94" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="E94:E102" si="164">SUMIFS(P:P,$M:$M,$A94)*$D94</f>
         <v>1.9344274695138082</v>
       </c>
       <c r="F94" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="F94:F102" si="165">SUMIFS(Q:Q,$M:$M,$A94)*$D94</f>
         <v>1.7309925752688549</v>
       </c>
       <c r="G94" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="G94:G102" si="166">SUMIFS(R:R,$M:$M,$A94)*$D94</f>
         <v>1.8060969503512614</v>
       </c>
       <c r="H94" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="H94:H102" si="167">SUMIFS(S:S,$M:$M,$A94)*$D94</f>
         <v>2.3602366221549298</v>
       </c>
       <c r="I94" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="I94:I102" si="168">SUMIFS(T:T,$M:$M,$A94)*$D94</f>
         <v>2.3951764836063103</v>
       </c>
       <c r="J94" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A94)*$D94</f>
+        <f t="shared" ref="J94:J102" si="169">SUMIFS(U:U,$M:$M,$A94)*$D94</f>
         <v>2.9127435901524592</v>
       </c>
       <c r="K94" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>26.646693938863347</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>18</v>
       </c>
@@ -5093,39 +5126,39 @@
         <v>21.629999999999956</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" ref="D95" si="127">C95/C103</f>
+        <f t="shared" ref="D95" si="170">C95/C103</f>
         <v>1.9266243812845734E-2</v>
       </c>
       <c r="E95" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="164"/>
         <v>3.1005310237557326</v>
       </c>
       <c r="F95" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="165"/>
         <v>2.7744623492452969</v>
       </c>
       <c r="G95" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="166"/>
         <v>2.8948408326119108</v>
       </c>
       <c r="H95" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="167"/>
         <v>3.7830246859734027</v>
       </c>
       <c r="I95" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="168"/>
         <v>3.8390268499743918</v>
       </c>
       <c r="J95" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A95)*$D95</f>
+        <f t="shared" si="169"/>
         <v>4.6685916157834466</v>
       </c>
       <c r="K95" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>42.709743601156994</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>18</v>
       </c>
@@ -5136,39 +5169,39 @@
         <v>7.400000000000001E-2</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" ref="D96" si="128">C96/C103</f>
+        <f t="shared" ref="D96" si="171">C96/C103</f>
         <v>6.5913178092953651E-5</v>
       </c>
       <c r="E96" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="164"/>
         <v>1.0607457039201329E-2</v>
       </c>
       <c r="F96" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="165"/>
         <v>9.4919192715743148E-3</v>
       </c>
       <c r="G96" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="166"/>
         <v>9.903755044534529E-3</v>
       </c>
       <c r="H96" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="167"/>
         <v>1.2942386812854019E-2</v>
       </c>
       <c r="I96" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="168"/>
         <v>1.3133979976796377E-2</v>
       </c>
       <c r="J96" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A96)*$D96</f>
+        <f t="shared" si="169"/>
         <v>1.5972065629587414E-2</v>
       </c>
       <c r="K96" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.14611747695264096</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>18</v>
       </c>
@@ -5179,39 +5212,39 @@
         <v>0</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" ref="D97" si="129">C97/C103</f>
+        <f t="shared" ref="D97" si="172">C97/C103</f>
         <v>0</v>
       </c>
       <c r="E97" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="F97" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="G97" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="166"/>
         <v>0</v>
       </c>
       <c r="H97" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="I97" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="J97" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A97)*$D97</f>
+        <f t="shared" si="169"/>
         <v>0</v>
       </c>
       <c r="K97" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>18</v>
       </c>
@@ -5222,39 +5255,39 @@
         <v>1.3750000000000002</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" ref="D98" si="130">C98/C103</f>
+        <f t="shared" ref="D98" si="173">C98/C103</f>
         <v>1.224738106456909E-3</v>
       </c>
       <c r="E98" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="164"/>
         <v>0.19709801930948415</v>
       </c>
       <c r="F98" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="165"/>
         <v>0.17637012160019841</v>
       </c>
       <c r="G98" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="166"/>
         <v>0.18402247548966186</v>
       </c>
       <c r="H98" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="167"/>
         <v>0.24048353875235506</v>
       </c>
       <c r="I98" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="168"/>
         <v>0.24404354686614887</v>
       </c>
       <c r="J98" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A98)*$D98</f>
+        <f t="shared" si="169"/>
         <v>0.29677824649571211</v>
       </c>
       <c r="K98" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>2.7150206866200177</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>18</v>
       </c>
@@ -5265,39 +5298,39 @@
         <v>308.48999999999984</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" ref="D99" si="131">C99/C103</f>
-        <v>0.2747777879715575</v>
+        <v>0.31887662573285219</v>
       </c>
       <c r="E99" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A99)*$D99</f>
-        <v>44.220194892205612</v>
+        <f t="shared" si="164"/>
+        <v>51.317053829457336</v>
       </c>
       <c r="F99" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A99)*$D99</f>
-        <v>39.569759136323754</v>
+        <f t="shared" si="165"/>
+        <v>45.920273860559305</v>
       </c>
       <c r="G99" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A99)*$D99</f>
-        <v>41.286613428222353</v>
+        <f t="shared" si="166"/>
+        <v>47.912664539285707</v>
       </c>
       <c r="H99" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A99)*$D99</f>
-        <v>53.954012268882877</v>
+        <f t="shared" si="167"/>
+        <v>62.613042721019177</v>
       </c>
       <c r="I99" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A99)*$D99</f>
-        <v>54.752722743809606</v>
+        <f t="shared" si="168"/>
+        <v>63.539937515035369</v>
       </c>
       <c r="J99" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A99)*$D99</f>
-        <v>66.58408819015429</v>
+        <f t="shared" si="169"/>
+        <v>77.270108061910776</v>
       </c>
       <c r="K99" s="16">
-        <f t="shared" si="86"/>
-        <v>609.13216844756982</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>657.38195715300026</v>
+      </c>
+      <c r="L99" s="19"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>18</v>
       </c>
@@ -5308,39 +5341,38 @@
         <v>776.15999999999985</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" ref="D100" si="132">C100/C103</f>
-        <v>0.69134016633279571</v>
+        <v>0.64724132857150107</v>
       </c>
       <c r="E100" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A100)*$D100</f>
-        <v>111.25788993981756</v>
+        <f t="shared" si="164"/>
+        <v>104.16103100256585</v>
       </c>
       <c r="F100" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A100)*$D100</f>
-        <v>99.557406240879956</v>
+        <f t="shared" si="165"/>
+        <v>93.206891516644419</v>
       </c>
       <c r="G100" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A100)*$D100</f>
-        <v>103.87700696440427</v>
+        <f t="shared" si="166"/>
+        <v>97.25095585334094</v>
       </c>
       <c r="H100" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A100)*$D100</f>
-        <v>135.74814795492932</v>
+        <f t="shared" si="167"/>
+        <v>127.08911750279303</v>
       </c>
       <c r="I100" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A100)*$D100</f>
-        <v>137.75770133500367</v>
+        <f t="shared" si="168"/>
+        <v>128.97048656377791</v>
       </c>
       <c r="J100" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A100)*$D100</f>
-        <v>167.52538458189949</v>
+        <f t="shared" si="169"/>
+        <v>156.83936471014303</v>
       </c>
       <c r="K100" s="16">
-        <f t="shared" si="86"/>
-        <v>1532.5748771832671</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>1484.3250884778365</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>18</v>
       </c>
@@ -5351,39 +5383,39 @@
         <v>0</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" ref="D101" si="133">C101/C103</f>
+        <f t="shared" ref="D101" si="174">C101/C103</f>
         <v>0</v>
       </c>
       <c r="E101" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="F101" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="G101" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="166"/>
         <v>0</v>
       </c>
       <c r="H101" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="I101" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="J101" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A101)*$D101</f>
+        <f t="shared" si="169"/>
         <v>0</v>
       </c>
       <c r="K101" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
         <v>18</v>
       </c>
@@ -5394,76 +5426,80 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" ref="D102" si="134">C102/C103</f>
+        <f t="shared" ref="D102" si="175">C102/C103</f>
         <v>1.3049027825159066E-3</v>
       </c>
       <c r="E102" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="164"/>
         <v>0.20999898057337762</v>
       </c>
       <c r="F102" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="165"/>
         <v>0.18791434774130231</v>
       </c>
       <c r="G102" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="166"/>
         <v>0.19606758297625787</v>
       </c>
       <c r="H102" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="167"/>
         <v>0.25622427947069099</v>
       </c>
       <c r="I102" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="168"/>
         <v>0.26001730629738773</v>
       </c>
       <c r="J102" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A102)*$D102</f>
+        <f t="shared" si="169"/>
         <v>0.31620373172088595</v>
       </c>
       <c r="K102" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>2.8927311315624187</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="19">
+        <f>1-D103</f>
+        <v>0</v>
+      </c>
       <c r="C103" s="3">
         <v>1122.6889999999996</v>
       </c>
       <c r="D103" s="5">
-        <f t="shared" ref="D103:E103" si="135">SUM(D94:D102)</f>
+        <f t="shared" ref="D103:E103" si="176">SUM(D94:D102)</f>
         <v>1</v>
       </c>
       <c r="E103" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="176"/>
         <v>160.93074778221478</v>
       </c>
       <c r="F103" s="9">
-        <f t="shared" ref="F103" si="136">SUM(F94:F102)</f>
-        <v>144.00639669033092</v>
+        <f t="shared" ref="F103" si="177">SUM(F94:F102)</f>
+        <v>144.00639669033094</v>
       </c>
       <c r="G103" s="9">
-        <f t="shared" ref="G103" si="137">SUM(G94:G102)</f>
-        <v>150.25455198910026</v>
+        <f t="shared" ref="G103" si="178">SUM(G94:G102)</f>
+        <v>150.25455198910029</v>
       </c>
       <c r="H103" s="9">
-        <f t="shared" ref="H103" si="138">SUM(H94:H102)</f>
-        <v>196.35507173697644</v>
+        <f t="shared" ref="H103" si="179">SUM(H94:H102)</f>
+        <v>196.35507173697647</v>
       </c>
       <c r="I103" s="9">
-        <f t="shared" ref="I103" si="139">SUM(I94:I102)</f>
+        <f t="shared" ref="I103" si="180">SUM(I94:I102)</f>
         <v>199.26182224553432</v>
       </c>
       <c r="J103" s="9">
-        <f t="shared" ref="J103" si="140">SUM(J94:J102)</f>
+        <f t="shared" ref="J103" si="181">SUM(J94:J102)</f>
         <v>242.31976202183588</v>
       </c>
       <c r="K103" s="18">
-        <f t="shared" si="86"/>
-        <v>2216.8173524659919</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>2216.8173524659924</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>19</v>
       </c>
@@ -5474,39 +5510,39 @@
         <v>25.739999999999988</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" ref="D104" si="141">C104/C113</f>
+        <f t="shared" ref="D104" si="182">C104/C113</f>
         <v>1.5234618450934061E-2</v>
       </c>
       <c r="E104" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="E104:E112" si="183">SUMIFS(P:P,$M:$M,$A104)*$D104</f>
         <v>3.6896749214735407</v>
       </c>
       <c r="F104" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="F104:F112" si="184">SUMIFS(Q:Q,$M:$M,$A104)*$D104</f>
         <v>3.301648676355712</v>
       </c>
       <c r="G104" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="G104:G112" si="185">SUMIFS(R:R,$M:$M,$A104)*$D104</f>
         <v>3.4449007411664674</v>
       </c>
       <c r="H104" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="H104:H112" si="186">SUMIFS(S:S,$M:$M,$A104)*$D104</f>
         <v>4.5018518454440839</v>
       </c>
       <c r="I104" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="I104:I112" si="187">SUMIFS(T:T,$M:$M,$A104)*$D104</f>
         <v>4.568495197334304</v>
       </c>
       <c r="J104" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A104)*$D104</f>
+        <f t="shared" ref="J104:J112" si="188">SUMIFS(U:U,$M:$M,$A104)*$D104</f>
         <v>5.5556887743997274</v>
       </c>
       <c r="K104" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>50.817494774624762</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>19</v>
       </c>
@@ -5517,39 +5553,39 @@
         <v>25.661999999999928</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" ref="D105" si="142">C105/C113</f>
+        <f t="shared" ref="D105" si="189">C105/C113</f>
         <v>1.518845294047665E-2</v>
       </c>
       <c r="E105" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="183"/>
         <v>3.6784940883781578</v>
       </c>
       <c r="F105" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="184"/>
         <v>3.2916436803667475</v>
       </c>
       <c r="G105" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="185"/>
         <v>3.4344616480114096</v>
       </c>
       <c r="H105" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="186"/>
         <v>4.488209870154849</v>
       </c>
       <c r="I105" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="187"/>
         <v>4.5546512724938868</v>
       </c>
       <c r="J105" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A105)*$D105</f>
+        <f t="shared" si="188"/>
         <v>5.5388533538712306</v>
       </c>
       <c r="K105" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>50.663502366216683</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>19</v>
       </c>
@@ -5560,39 +5596,39 @@
         <v>0.11600000000000003</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" ref="D106" si="143">C106/C113</f>
+        <f t="shared" ref="D106" si="190">C106/C113</f>
         <v>6.8656400167379662E-5</v>
       </c>
       <c r="E106" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="183"/>
         <v>1.6627905629018301E-2</v>
       </c>
       <c r="F106" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="184"/>
         <v>1.4879224804089469E-2</v>
       </c>
       <c r="G106" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="185"/>
         <v>1.5524805204946019E-2</v>
       </c>
       <c r="H106" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="186"/>
         <v>2.0288065814744138E-2</v>
       </c>
       <c r="I106" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="187"/>
         <v>2.0588401044707837E-2</v>
       </c>
       <c r="J106" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A106)*$D106</f>
+        <f t="shared" si="188"/>
         <v>2.5037292068001898E-2</v>
       </c>
       <c r="K106" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.22901435096567505</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>19</v>
       </c>
@@ -5603,39 +5639,39 @@
         <v>0</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" ref="D107" si="144">C107/C113</f>
+        <f t="shared" ref="D107" si="191">C107/C113</f>
         <v>0</v>
       </c>
       <c r="E107" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="F107" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="G107" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H107" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="I107" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J107" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A107)*$D107</f>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="K107" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>19</v>
       </c>
@@ -5646,39 +5682,39 @@
         <v>3.3250000000000006</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" ref="D108" si="145">C108/C113</f>
+        <f t="shared" ref="D108" si="192">C108/C113</f>
         <v>1.9679528496253217E-3</v>
       </c>
       <c r="E108" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="183"/>
         <v>0.47661884669384341</v>
       </c>
       <c r="F108" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="184"/>
         <v>0.4264950213241161</v>
       </c>
       <c r="G108" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="185"/>
         <v>0.44499980436590952</v>
       </c>
       <c r="H108" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="186"/>
         <v>0.5815329209829676</v>
       </c>
       <c r="I108" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="187"/>
         <v>0.59014166787632361</v>
       </c>
       <c r="J108" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A108)*$D108</f>
+        <f t="shared" si="188"/>
         <v>0.71766375970781293</v>
       </c>
       <c r="K108" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>6.5644199738005984</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>19</v>
       </c>
@@ -5689,39 +5725,39 @@
         <v>574.03999999999826</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" ref="D109" si="146">C109/C113</f>
-        <v>0.33975448234553868</v>
+        <v>0.33370187775237187</v>
       </c>
       <c r="E109" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A109)*$D109</f>
-        <v>82.285197821393396</v>
+        <f t="shared" si="183"/>
+        <v>80.819316450689684</v>
       </c>
       <c r="F109" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A109)*$D109</f>
-        <v>73.631639711547322</v>
+        <f t="shared" si="184"/>
+        <v>72.31991838371134</v>
       </c>
       <c r="G109" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A109)*$D109</f>
-        <v>76.826372240061914</v>
+        <f t="shared" si="185"/>
+        <v>75.457737894794846</v>
       </c>
       <c r="H109" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A109)*$D109</f>
-        <v>100.39794224392833</v>
+        <f t="shared" si="186"/>
+        <v>98.609388809180459</v>
       </c>
       <c r="I109" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A109)*$D109</f>
-        <v>101.88418737675902</v>
+        <f t="shared" si="187"/>
+        <v>100.0691570165106</v>
       </c>
       <c r="J109" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A109)*$D109</f>
-        <v>123.90006154065311</v>
+        <f t="shared" si="188"/>
+        <v>121.69282625593384</v>
       </c>
       <c r="K109" s="16">
-        <f t="shared" si="86"/>
-        <v>1133.3051554166868</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>1123.3420466885714</v>
+      </c>
+      <c r="L109" s="19"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>19</v>
       </c>
@@ -5732,39 +5768,38 @@
         <v>1060.69</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" ref="D110" si="147">C110/C113</f>
-        <v>0.62778583701325785</v>
+        <v>0.63383844160642466</v>
       </c>
       <c r="E110" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A110)*$D110</f>
-        <v>152.0435622555467</v>
+        <f t="shared" si="183"/>
+        <v>153.5094436262504</v>
       </c>
       <c r="F110" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A110)*$D110</f>
-        <v>136.05383584008322</v>
+        <f t="shared" si="184"/>
+        <v>137.36555716791918</v>
       </c>
       <c r="G110" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A110)*$D110</f>
-        <v>141.95694511063957</v>
+        <f t="shared" si="185"/>
+        <v>143.32557945590662</v>
       </c>
       <c r="H110" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A110)*$D110</f>
-        <v>185.51162525035306</v>
+        <f t="shared" si="186"/>
+        <v>187.30017868510092</v>
       </c>
       <c r="I110" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A110)*$D110</f>
-        <v>188.25785434578577</v>
+        <f t="shared" si="187"/>
+        <v>190.07288470603419</v>
       </c>
       <c r="J110" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A110)*$D110</f>
-        <v>228.93797692766316</v>
+        <f t="shared" si="188"/>
+        <v>231.14521221238243</v>
       </c>
       <c r="K110" s="16">
-        <f t="shared" si="86"/>
-        <v>2094.0795855670849</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>2104.0426942952004</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>19</v>
       </c>
@@ -5775,39 +5810,39 @@
         <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" ref="D111" si="148">C111/C113</f>
+        <f t="shared" ref="D111" si="193">C111/C113</f>
         <v>0</v>
       </c>
       <c r="E111" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="F111" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="G111" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H111" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="I111" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J111" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A111)*$D111</f>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="K111" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
         <v>19</v>
       </c>
@@ -5818,76 +5853,80 @@
         <v>0</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" ref="D112" si="149">C112/C113</f>
+        <f t="shared" ref="D112" si="194">C112/C113</f>
         <v>0</v>
       </c>
       <c r="E112" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="F112" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="G112" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H112" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="I112" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J112" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A112)*$D112</f>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="K112" s="17">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="19">
+        <f>1-D113</f>
+        <v>0</v>
+      </c>
       <c r="C113" s="3">
         <v>1689.5729999999983</v>
       </c>
       <c r="D113" s="5">
-        <f t="shared" ref="D113:E113" si="150">SUM(D104:D112)</f>
+        <f t="shared" ref="D113:E113" si="195">SUM(D104:D112)</f>
         <v>1</v>
       </c>
       <c r="E113" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="195"/>
         <v>242.19017583911466</v>
       </c>
       <c r="F113" s="9">
-        <f t="shared" ref="F113" si="151">SUM(F104:F112)</f>
-        <v>216.72014215448121</v>
+        <f t="shared" ref="F113" si="196">SUM(F104:F112)</f>
+        <v>216.72014215448118</v>
       </c>
       <c r="G113" s="9">
-        <f t="shared" ref="G113" si="152">SUM(G104:G112)</f>
-        <v>226.12320434945022</v>
+        <f t="shared" ref="G113" si="197">SUM(G104:G112)</f>
+        <v>226.12320434945019</v>
       </c>
       <c r="H113" s="9">
-        <f t="shared" ref="H113" si="153">SUM(H104:H112)</f>
+        <f t="shared" ref="H113" si="198">SUM(H104:H112)</f>
         <v>295.50145019667804</v>
       </c>
       <c r="I113" s="9">
-        <f t="shared" ref="I113" si="154">SUM(I104:I112)</f>
+        <f t="shared" ref="I113" si="199">SUM(I104:I112)</f>
         <v>299.87591826129403</v>
       </c>
       <c r="J113" s="9">
-        <f t="shared" ref="J113" si="155">SUM(J104:J112)</f>
+        <f t="shared" ref="J113" si="200">SUM(J104:J112)</f>
         <v>364.67528164836301</v>
       </c>
       <c r="K113" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>3335.6591724493792</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>20</v>
       </c>
@@ -5898,39 +5937,39 @@
         <v>23.924999999999997</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" ref="D114" si="156">C114/C123</f>
+        <f t="shared" ref="D114" si="201">C114/C123</f>
         <v>1.0022890312504711E-2</v>
       </c>
       <c r="E114" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="E114:E122" si="202">SUMIFS(P:P,$M:$M,$A114)*$D114</f>
         <v>3.4295055359850224</v>
       </c>
       <c r="F114" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="F114:F122" si="203">SUMIFS(Q:Q,$M:$M,$A114)*$D114</f>
         <v>3.0688401158434515</v>
       </c>
       <c r="G114" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="G114:G122" si="204">SUMIFS(R:R,$M:$M,$A114)*$D114</f>
         <v>3.2019910735201145</v>
       </c>
       <c r="H114" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="H114:H122" si="205">SUMIFS(S:S,$M:$M,$A114)*$D114</f>
         <v>4.1844135742909767</v>
       </c>
       <c r="I114" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="I114:I122" si="206">SUMIFS(T:T,$M:$M,$A114)*$D114</f>
         <v>4.2463577154709897</v>
       </c>
       <c r="J114" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A114)*$D114</f>
+        <f t="shared" ref="J114:J122" si="207">SUMIFS(U:U,$M:$M,$A114)*$D114</f>
         <v>5.1639414890253894</v>
       </c>
       <c r="K114" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>47.230072394448449</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>20</v>
       </c>
@@ -5941,39 +5980,39 @@
         <v>30.445999999999998</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" ref="D115" si="157">C115/C123</f>
+        <f t="shared" ref="D115" si="208">C115/C123</f>
         <v>1.2754730133940165E-2</v>
       </c>
       <c r="E115" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="202"/>
         <v>4.3642518515611286</v>
       </c>
       <c r="F115" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="203"/>
         <v>3.9052834343561016</v>
       </c>
       <c r="G115" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="204"/>
         <v>4.0747260281878122</v>
       </c>
       <c r="H115" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="205"/>
         <v>5.3249176878939632</v>
       </c>
       <c r="I115" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="206"/>
         <v>5.4037453293721951</v>
       </c>
       <c r="J115" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A115)*$D115</f>
+        <f t="shared" si="207"/>
         <v>6.571425812951599</v>
       </c>
       <c r="K115" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>60.103104874456733</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>20</v>
       </c>
@@ -5984,39 +6023,39 @@
         <v>0.125</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" ref="D116" si="158">C116/C123</f>
+        <f t="shared" ref="D116" si="209">C116/C123</f>
         <v>5.2366198079961924E-5</v>
       </c>
       <c r="E116" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="202"/>
         <v>1.7918001755407642E-2</v>
       </c>
       <c r="F116" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="203"/>
         <v>1.6033647418199851E-2</v>
       </c>
       <c r="G116" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="204"/>
         <v>1.6729315953605616E-2</v>
       </c>
       <c r="H116" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="205"/>
         <v>2.1862139886577727E-2</v>
       </c>
       <c r="I116" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="206"/>
         <v>2.2185776987831713E-2</v>
       </c>
       <c r="J116" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A116)*$D116</f>
+        <f t="shared" si="207"/>
         <v>2.6979840590519277E-2</v>
       </c>
       <c r="K116" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.24676108879022179</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>20</v>
       </c>
@@ -6027,39 +6066,39 @@
         <v>0</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" ref="D117" si="159">C117/C123</f>
+        <f t="shared" ref="D117" si="210">C117/C123</f>
         <v>0</v>
       </c>
       <c r="E117" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="F117" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="203"/>
         <v>0</v>
       </c>
       <c r="G117" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="H117" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="I117" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
       <c r="J117" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A117)*$D117</f>
+        <f t="shared" si="207"/>
         <v>0</v>
       </c>
       <c r="K117" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>20</v>
       </c>
@@ -6070,39 +6109,39 @@
         <v>0.57499999999999996</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" ref="D118" si="160">C118/C123</f>
+        <f t="shared" ref="D118" si="211">C118/C123</f>
         <v>2.4088451116782483E-4</v>
       </c>
       <c r="E118" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="202"/>
         <v>8.2422808074875148E-2</v>
       </c>
       <c r="F118" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="203"/>
         <v>7.375477812371932E-2</v>
       </c>
       <c r="G118" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="204"/>
         <v>7.6954853386585836E-2</v>
       </c>
       <c r="H118" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="205"/>
         <v>0.10056584347825753</v>
       </c>
       <c r="I118" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="206"/>
         <v>0.10205457414402588</v>
       </c>
       <c r="J118" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A118)*$D118</f>
+        <f t="shared" si="207"/>
         <v>0.12410726671638866</v>
       </c>
       <c r="K118" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>1.1351010084350202</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>20</v>
       </c>
@@ -6113,39 +6152,39 @@
         <v>619.32499999999993</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" ref="D119" si="161">C119/C123</f>
-        <v>0.25945356500697936</v>
+        <v>0.32184851227247274</v>
       </c>
       <c r="E119" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A119)*$D119</f>
-        <v>88.776531497342717</v>
+        <f t="shared" si="202"/>
+        <v>110.12604350362832</v>
       </c>
       <c r="F119" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A119)*$D119</f>
-        <v>79.440309498212997</v>
+        <f t="shared" si="203"/>
+        <v>98.544590920447973</v>
       </c>
       <c r="G119" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A119)*$D119</f>
-        <v>82.887068823734396</v>
+        <f t="shared" si="204"/>
+        <v>102.82024757234441</v>
       </c>
       <c r="H119" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A119)*$D119</f>
-        <v>108.31815828203801</v>
+        <f t="shared" si="205"/>
+        <v>134.36715773872817</v>
       </c>
       <c r="I119" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A119)*$D119</f>
-        <v>109.92165066391101</v>
+        <f t="shared" si="206"/>
+        <v>136.35626757243651</v>
       </c>
       <c r="J119" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A119)*$D119</f>
-        <v>133.67431818978682</v>
+        <f t="shared" si="207"/>
+        <v>165.821118847462</v>
       </c>
       <c r="K119" s="16">
-        <f t="shared" si="86"/>
-        <v>1222.6024905200329</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>1367.6822746673199</v>
+      </c>
+      <c r="L119" s="19"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>20</v>
       </c>
@@ -6156,39 +6195,38 @@
         <v>1712.6000000000001</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" ref="D120" si="162">C120/C123</f>
-        <v>0.71745880665394246</v>
+        <v>0.65506385938844902</v>
       </c>
       <c r="E120" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A120)*$D120</f>
-        <v>245.49095845048907</v>
+        <f t="shared" si="202"/>
+        <v>224.14144644420344</v>
       </c>
       <c r="F120" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A120)*$D120</f>
-        <v>219.67379654727259</v>
+        <f t="shared" si="203"/>
+        <v>200.56951512503758</v>
       </c>
       <c r="G120" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A120)*$D120</f>
-        <v>229.20501201715987</v>
+        <f t="shared" si="204"/>
+        <v>209.27183326854984</v>
       </c>
       <c r="H120" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A120)*$D120</f>
-        <v>299.52880615802417</v>
+        <f t="shared" si="205"/>
+        <v>273.47980670133398</v>
       </c>
       <c r="I120" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A120)*$D120</f>
-        <v>303.96289335488478</v>
+        <f t="shared" si="206"/>
+        <v>277.52827644635931</v>
       </c>
       <c r="J120" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A120)*$D120</f>
-        <v>369.64539996258657</v>
+        <f t="shared" si="207"/>
+        <v>337.49859930491141</v>
       </c>
       <c r="K120" s="16">
-        <f t="shared" si="86"/>
-        <v>3380.8243252970706</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>3235.7445411497838</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>20</v>
       </c>
@@ -6199,39 +6237,39 @@
         <v>0</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" ref="D121" si="163">C121/C123</f>
+        <f t="shared" ref="D121" si="212">C121/C123</f>
         <v>0</v>
       </c>
       <c r="E121" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="F121" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="203"/>
         <v>0</v>
       </c>
       <c r="G121" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="H121" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="I121" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
       <c r="J121" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A121)*$D121</f>
+        <f t="shared" si="207"/>
         <v>0</v>
       </c>
       <c r="K121" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>20</v>
       </c>
@@ -6242,76 +6280,80 @@
         <v>0.04</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" ref="D122" si="164">C122/C123</f>
+        <f t="shared" ref="D122" si="213">C122/C123</f>
         <v>1.6757183385587818E-5</v>
       </c>
       <c r="E122" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="202"/>
         <v>5.733760561730447E-3</v>
       </c>
       <c r="F122" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="203"/>
         <v>5.130767173823954E-3</v>
       </c>
       <c r="G122" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="204"/>
         <v>5.3533811051537979E-3</v>
       </c>
       <c r="H122" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="205"/>
         <v>6.9958847637048736E-3</v>
       </c>
       <c r="I122" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="206"/>
         <v>7.0994486361061499E-3</v>
       </c>
       <c r="J122" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A122)*$D122</f>
+        <f t="shared" si="207"/>
         <v>8.6335489889661707E-3</v>
       </c>
       <c r="K122" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>7.8963548412870982E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="19">
+        <f>1-D123</f>
+        <v>0</v>
+      </c>
       <c r="C123" s="3">
         <v>2387.0360000000001</v>
       </c>
       <c r="D123" s="5">
-        <f t="shared" ref="D123:E123" si="165">SUM(D114:D122)</f>
+        <f t="shared" ref="D123:E123" si="214">SUM(D114:D122)</f>
         <v>1</v>
       </c>
       <c r="E123" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="214"/>
         <v>342.16732190576994</v>
       </c>
       <c r="F123" s="9">
-        <f t="shared" ref="F123" si="166">SUM(F114:F122)</f>
+        <f t="shared" ref="F123" si="215">SUM(F114:F122)</f>
         <v>306.18314878840084</v>
       </c>
       <c r="G123" s="9">
-        <f t="shared" ref="G123" si="167">SUM(G114:G122)</f>
+        <f t="shared" ref="G123" si="216">SUM(G114:G122)</f>
         <v>319.46783549304757</v>
       </c>
       <c r="H123" s="9">
-        <f t="shared" ref="H123" si="168">SUM(H114:H122)</f>
+        <f t="shared" ref="H123" si="217">SUM(H114:H122)</f>
         <v>417.48571957037564</v>
       </c>
       <c r="I123" s="9">
-        <f t="shared" ref="I123" si="169">SUM(I114:I122)</f>
-        <v>423.66598686340694</v>
+        <f t="shared" ref="I123" si="218">SUM(I114:I122)</f>
+        <v>423.665986863407</v>
       </c>
       <c r="J123" s="9">
-        <f t="shared" ref="J123" si="170">SUM(J114:J122)</f>
+        <f t="shared" ref="J123" si="219">SUM(J114:J122)</f>
         <v>515.21480611064624</v>
       </c>
       <c r="K123" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>4712.2208187316473</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>21</v>
       </c>
@@ -6322,39 +6364,39 @@
         <v>42.870000000000005</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" ref="D124" si="171">C124/C133</f>
+        <f t="shared" ref="D124" si="220">C124/C133</f>
         <v>3.9727837899300933E-3</v>
       </c>
       <c r="E124" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="E124:E132" si="221">SUMIFS(P:P,$M:$M,$A124)*$D124</f>
         <v>6.1451578820346056</v>
       </c>
       <c r="F124" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="F124:F132" si="222">SUMIFS(Q:Q,$M:$M,$A124)*$D124</f>
         <v>5.4988997185458226</v>
       </c>
       <c r="G124" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="G124:G132" si="223">SUMIFS(R:R,$M:$M,$A124)*$D124</f>
         <v>5.7374861994485835</v>
       </c>
       <c r="H124" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="H124:H132" si="224">SUMIFS(S:S,$M:$M,$A124)*$D124</f>
         <v>7.4978394955006982</v>
       </c>
       <c r="I124" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="I124:I132" si="225">SUMIFS(T:T,$M:$M,$A124)*$D124</f>
         <v>7.6088340757467652</v>
       </c>
       <c r="J124" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A124)*$D124</f>
+        <f t="shared" ref="J124:J132" si="226">SUMIFS(U:U,$M:$M,$A124)*$D124</f>
         <v>9.2530061289244916</v>
       </c>
       <c r="K124" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>84.615196283990912</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>21</v>
       </c>
@@ -6365,39 +6407,39 @@
         <v>86.950000000000173</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" ref="D125" si="172">C125/C133</f>
+        <f t="shared" ref="D125" si="227">C125/C133</f>
         <v>8.0576988694756775E-3</v>
       </c>
       <c r="E125" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="221"/>
         <v>12.463762021061582</v>
       </c>
       <c r="F125" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="222"/>
         <v>11.153005144099842</v>
       </c>
       <c r="G125" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="223"/>
         <v>11.636912177328092</v>
       </c>
       <c r="H125" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="224"/>
         <v>15.207304505103499</v>
       </c>
       <c r="I125" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="225"/>
         <v>15.432426472735772</v>
       </c>
       <c r="J125" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A125)*$D125</f>
+        <f t="shared" si="226"/>
         <v>18.767177114765246</v>
       </c>
       <c r="K125" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>171.6186451339637</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>21</v>
       </c>
@@ -6408,39 +6450,39 @@
         <v>0.27700000000000008</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" ref="D126" si="173">C126/C133</f>
+        <f t="shared" ref="D126" si="228">C126/C133</f>
         <v>2.5669724978088082E-5</v>
       </c>
       <c r="E126" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="221"/>
         <v>3.9706291889983349E-2</v>
       </c>
       <c r="F126" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="222"/>
         <v>3.5530562678730886E-2</v>
       </c>
       <c r="G126" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="223"/>
         <v>3.7072164153190063E-2</v>
       </c>
       <c r="H126" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="224"/>
         <v>4.8446501988656257E-2</v>
       </c>
       <c r="I126" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="225"/>
         <v>4.9163681805035095E-2</v>
       </c>
       <c r="J126" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A126)*$D126</f>
+        <f t="shared" si="226"/>
         <v>5.9787326748590726E-2</v>
       </c>
       <c r="K126" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.54673219898916459</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>21</v>
       </c>
@@ -6451,39 +6493,39 @@
         <v>0</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" ref="D127" si="174">C127/C133</f>
+        <f t="shared" ref="D127" si="229">C127/C133</f>
         <v>0</v>
       </c>
       <c r="E127" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
       <c r="F127" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="G127" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="223"/>
         <v>0</v>
       </c>
       <c r="H127" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="224"/>
         <v>0</v>
       </c>
       <c r="I127" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="J127" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A127)*$D127</f>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="K127" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>21</v>
       </c>
@@ -6494,39 +6536,39 @@
         <v>14.299999999999999</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" ref="D128" si="175">C128/C133</f>
+        <f t="shared" ref="D128" si="230">C128/C133</f>
         <v>1.3251879681828861E-3</v>
       </c>
       <c r="E128" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="221"/>
         <v>2.0498194008186346</v>
       </c>
       <c r="F128" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="222"/>
         <v>1.8342492646420632</v>
       </c>
       <c r="G128" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="223"/>
         <v>1.9138337450924827</v>
       </c>
       <c r="H128" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="224"/>
         <v>2.501028803024492</v>
       </c>
       <c r="I128" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="225"/>
         <v>2.538052887407948</v>
       </c>
       <c r="J128" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A128)*$D128</f>
+        <f t="shared" si="226"/>
         <v>3.0864937635554051</v>
       </c>
       <c r="K128" s="16">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>28.224803052509209</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>21</v>
       </c>
@@ -6537,39 +6579,39 @@
         <v>2186.8750000000077</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" ref="D129" si="176">C129/C133</f>
-        <v>0.20265877188251466</v>
+        <v>0.28519178672932394</v>
       </c>
       <c r="E129" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A129)*$D129</f>
-        <v>313.47544071085787</v>
+        <f t="shared" si="221"/>
+        <v>441.13866970396492</v>
       </c>
       <c r="F129" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A129)*$D129</f>
-        <v>280.50866158140747</v>
+        <f t="shared" si="222"/>
+        <v>394.74613236001323</v>
       </c>
       <c r="G129" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A129)*$D129</f>
-        <v>292.67938260833137</v>
+        <f t="shared" si="223"/>
+        <v>411.8733933377161</v>
       </c>
       <c r="H129" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A129)*$D129</f>
-        <v>382.47813731567874</v>
+        <f t="shared" si="224"/>
+        <v>538.24279281233271</v>
       </c>
       <c r="I129" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A129)*$D129</f>
-        <v>388.14016840211724</v>
+        <f t="shared" si="225"/>
+        <v>546.21069248456831</v>
       </c>
       <c r="J129" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A129)*$D129</f>
-        <v>472.01231113113641</v>
+        <f t="shared" si="226"/>
+        <v>664.23986052656426</v>
       </c>
       <c r="K129" s="16">
-        <f t="shared" si="86"/>
-        <v>4316.3717605214197</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>5183.6117330118968</v>
+      </c>
+      <c r="L129" s="19"/>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>21</v>
       </c>
@@ -6580,39 +6622,38 @@
         <v>8459.3499999999876</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" ref="D130" si="177">C130/C133</f>
-        <v>0.78393208661873304</v>
+        <v>0.70139907177192362</v>
       </c>
       <c r="E130" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A130)*$D130</f>
-        <v>1212.5971851968595</v>
+        <f t="shared" si="221"/>
+        <v>1084.9339562037524</v>
       </c>
       <c r="F130" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A130)*$D130</f>
-        <v>1085.07388229719</v>
+        <f t="shared" si="222"/>
+        <v>970.83641151858399</v>
       </c>
       <c r="G130" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A130)*$D130</f>
-        <v>1132.1531112970679</v>
+        <f t="shared" si="223"/>
+        <v>1012.959100567683</v>
       </c>
       <c r="H130" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A130)*$D130</f>
-        <v>1479.5159443961684</v>
+        <f t="shared" si="224"/>
+        <v>1323.7512888995143</v>
       </c>
       <c r="I130" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A130)*$D130</f>
-        <v>1501.4180204961117</v>
+        <f t="shared" si="225"/>
+        <v>1343.3474964136603</v>
       </c>
       <c r="J130" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A130)*$D130</f>
-        <v>1825.8553159952712</v>
+        <f t="shared" si="226"/>
+        <v>1633.627766599843</v>
       </c>
       <c r="K130" s="16">
-        <f t="shared" si="86"/>
-        <v>16696.747391765275</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>15829.507419274794</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>21</v>
       </c>
@@ -6623,39 +6664,39 @@
         <v>0</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" ref="D131" si="178">C131/C133</f>
+        <f t="shared" ref="D131" si="231">C131/C133</f>
         <v>0</v>
       </c>
       <c r="E131" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
       <c r="F131" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="G131" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="223"/>
         <v>0</v>
       </c>
       <c r="H131" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="224"/>
         <v>0</v>
       </c>
       <c r="I131" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="J131" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A131)*$D131</f>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="K131" s="16">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>21</v>
       </c>
@@ -6666,76 +6707,80 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" ref="D132" si="179">C132/C133</f>
+        <f t="shared" ref="D132" si="232">C132/C133</f>
         <v>2.7801146185654958E-5</v>
       </c>
       <c r="E132" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="221"/>
         <v>4.3003204212978353E-2</v>
       </c>
       <c r="F132" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="222"/>
         <v>3.8480753803679657E-2</v>
       </c>
       <c r="G132" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="223"/>
         <v>4.0150358288653487E-2</v>
       </c>
       <c r="H132" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="224"/>
         <v>5.2469135727786553E-2</v>
       </c>
       <c r="I132" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="225"/>
         <v>5.3245864770796118E-2</v>
       </c>
       <c r="J132" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A132)*$D132</f>
+        <f t="shared" si="226"/>
         <v>6.4751617417246263E-2</v>
       </c>
       <c r="K132" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="115"/>
         <v>0.59212873536732613</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B133" s="19">
+        <f>1-D133</f>
+        <v>0</v>
+      </c>
       <c r="C133" s="3">
         <v>10790.921999999995</v>
       </c>
       <c r="D133" s="5">
-        <f t="shared" ref="D133:E133" si="180">SUM(D124:D132)</f>
+        <f t="shared" ref="D133:E133" si="233">SUM(D124:D132)</f>
         <v>1</v>
       </c>
       <c r="E133" s="9">
-        <f t="shared" si="180"/>
-        <v>1546.8140747077352</v>
+        <f t="shared" si="233"/>
+        <v>1546.814074707735</v>
       </c>
       <c r="F133" s="9">
-        <f t="shared" ref="F133" si="181">SUM(F124:F132)</f>
-        <v>1384.1427093223676</v>
+        <f t="shared" ref="F133" si="234">SUM(F124:F132)</f>
+        <v>1384.1427093223674</v>
       </c>
       <c r="G133" s="9">
-        <f t="shared" ref="G133" si="182">SUM(G124:G132)</f>
+        <f t="shared" ref="G133" si="235">SUM(G124:G132)</f>
         <v>1444.1979485497102</v>
       </c>
       <c r="H133" s="9">
-        <f t="shared" ref="H133" si="183">SUM(H124:H132)</f>
-        <v>1887.3011701531923</v>
+        <f t="shared" ref="H133" si="236">SUM(H124:H132)</f>
+        <v>1887.3011701531921</v>
       </c>
       <c r="I133" s="9">
-        <f t="shared" ref="I133" si="184">SUM(I124:I132)</f>
-        <v>1915.2399118806952</v>
+        <f t="shared" ref="I133" si="237">SUM(I124:I132)</f>
+        <v>1915.239911880695</v>
       </c>
       <c r="J133" s="9">
-        <f t="shared" ref="J133" si="185">SUM(J124:J132)</f>
+        <f t="shared" ref="J133" si="238">SUM(J124:J132)</f>
         <v>2329.0988430778184</v>
       </c>
       <c r="K133" s="18">
-        <f t="shared" ref="K133:K142" si="186">SUM(C133:J133)</f>
-        <v>21298.716657691515</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K133:K142" si="239">SUM(C133:J133)</f>
+        <v>21298.716657691512</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>22</v>
       </c>
@@ -6746,39 +6791,39 @@
         <v>10.709999999999999</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" ref="D134" si="187">C134/C143</f>
+        <f t="shared" ref="D134" si="240">C134/C143</f>
         <v>3.3606652799346307E-3</v>
       </c>
       <c r="E134" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="E134:E142" si="241">SUMIFS(P:P,$M:$M,$A134)*$D134</f>
         <v>1.5352143904033266</v>
       </c>
       <c r="F134" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="F134:F142" si="242">SUMIFS(Q:Q,$M:$M,$A134)*$D134</f>
         <v>1.3737629107913631</v>
       </c>
       <c r="G134" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="G134:G142" si="243">SUMIFS(R:R,$M:$M,$A134)*$D134</f>
         <v>1.4333677909049289</v>
       </c>
       <c r="H134" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="H134:H142" si="244">SUMIFS(S:S,$M:$M,$A134)*$D134</f>
         <v>1.8731481454819792</v>
       </c>
       <c r="I134" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="I134:I142" si="245">SUMIFS(T:T,$M:$M,$A134)*$D134</f>
         <v>1.9008773723174208</v>
       </c>
       <c r="J134" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A134)*$D134</f>
+        <f t="shared" ref="J134:J142" si="246">SUMIFS(U:U,$M:$M,$A134)*$D134</f>
         <v>2.311632741795691</v>
       </c>
       <c r="K134" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="239"/>
         <v>21.141364016974645</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>22</v>
       </c>
@@ -6789,39 +6834,39 @@
         <v>23.149999999999988</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" ref="D135" si="188">C135/C143</f>
+        <f t="shared" ref="D135" si="247">C135/C143</f>
         <v>7.264183121427327E-3</v>
       </c>
       <c r="E135" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="241"/>
         <v>3.3184139251014941</v>
       </c>
       <c r="F135" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="242"/>
         <v>2.969431501850611</v>
       </c>
       <c r="G135" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="243"/>
         <v>3.0982693146077587</v>
       </c>
       <c r="H135" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="244"/>
         <v>4.0488683069941924</v>
       </c>
       <c r="I135" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="245"/>
         <v>4.1088058981464313</v>
       </c>
       <c r="J135" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A135)*$D135</f>
+        <f t="shared" si="246"/>
         <v>4.9966664773641671</v>
       </c>
       <c r="K135" s="16">
-        <f t="shared" si="186"/>
+        <f t="shared" si="239"/>
         <v>45.697719607186066</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
         <v>22</v>
       </c>
@@ -6832,39 +6877,39 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" ref="D136" si="189">C136/C143</f>
+        <f t="shared" ref="D136" si="248">C136/C143</f>
         <v>8.1270990429791742E-5</v>
       </c>
       <c r="E136" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="241"/>
         <v>3.7126099637204639E-2</v>
       </c>
       <c r="F136" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="242"/>
         <v>3.3221717450510092E-2</v>
       </c>
       <c r="G136" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="243"/>
         <v>3.4663142655870838E-2</v>
       </c>
       <c r="H136" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="244"/>
         <v>4.529835384498905E-2</v>
       </c>
       <c r="I136" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="245"/>
         <v>4.5968929918787309E-2</v>
       </c>
       <c r="J136" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A136)*$D136</f>
+        <f t="shared" si="246"/>
         <v>5.5902229703555947E-2</v>
       </c>
       <c r="K136" s="16">
-        <f t="shared" si="186"/>
+        <f t="shared" si="239"/>
         <v>0.51126174420134773</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>22</v>
       </c>
@@ -6875,39 +6920,39 @@
         <v>0</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" ref="D137" si="190">C137/C143</f>
+        <f t="shared" ref="D137" si="249">C137/C143</f>
         <v>0</v>
       </c>
       <c r="E137" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="241"/>
         <v>0</v>
       </c>
       <c r="F137" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="G137" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="H137" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="244"/>
         <v>0</v>
       </c>
       <c r="I137" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="J137" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A137)*$D137</f>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K137" s="16">
-        <f t="shared" si="186"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>22</v>
       </c>
@@ -6918,39 +6963,39 @@
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" ref="D138" si="191">C138/C143</f>
+        <f t="shared" ref="D138" si="250">C138/C143</f>
         <v>0</v>
       </c>
       <c r="E138" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="241"/>
         <v>0</v>
       </c>
       <c r="F138" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="G138" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="H138" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="244"/>
         <v>0</v>
       </c>
       <c r="I138" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="J138" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A138)*$D138</f>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K138" s="16">
-        <f t="shared" si="186"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>22</v>
       </c>
@@ -6961,39 +7006,39 @@
         <v>798.79999999999961</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" ref="D139" si="192">C139/C143</f>
-        <v>0.25065354114022242</v>
+        <v>0.27414625243546881</v>
       </c>
       <c r="E139" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A139)*$D139</f>
-        <v>114.50319841775696</v>
+        <f t="shared" si="241"/>
+        <v>125.23510577711009</v>
       </c>
       <c r="F139" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A139)*$D139</f>
-        <v>102.46142046126428</v>
+        <f t="shared" si="242"/>
+        <v>112.06470218171178</v>
       </c>
       <c r="G139" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A139)*$D139</f>
-        <v>106.90702066992128</v>
+        <f t="shared" si="243"/>
+        <v>116.92696996171436</v>
       </c>
       <c r="H139" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A139)*$D139</f>
-        <v>139.70781873118622</v>
+        <f t="shared" si="244"/>
+        <v>152.80205006025517</v>
       </c>
       <c r="I139" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A139)*$D139</f>
-        <v>141.77598926303972</v>
+        <f t="shared" si="245"/>
+        <v>155.06406159269116</v>
       </c>
       <c r="J139" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A139)*$D139</f>
-        <v>172.41197330965429</v>
+        <f t="shared" si="246"/>
+        <v>188.5714286853177</v>
       </c>
       <c r="K139" s="16">
-        <f t="shared" si="186"/>
-        <v>1576.8180743939627</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>1649.7384645112352</v>
+      </c>
+      <c r="L139" s="19"/>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>22</v>
       </c>
@@ -7004,39 +7049,38 @@
         <v>2353.9500000000007</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" ref="D140" si="193">C140/C143</f>
-        <v>0.7386403394679858</v>
+        <v>0.71514762817273947</v>
       </c>
       <c r="E140" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A140)*$D140</f>
-        <v>337.4246418571347</v>
+        <f t="shared" si="241"/>
+        <v>326.6927344977816</v>
       </c>
       <c r="F140" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A140)*$D140</f>
-        <v>301.93923472057241</v>
+        <f t="shared" si="242"/>
+        <v>292.33595300012496</v>
       </c>
       <c r="G140" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A140)*$D140</f>
-        <v>315.03978631191961</v>
+        <f t="shared" si="243"/>
+        <v>305.0198370201266</v>
       </c>
       <c r="H140" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A140)*$D140</f>
-        <v>411.6990734880772</v>
+        <f t="shared" si="244"/>
+        <v>398.60484215900829</v>
       </c>
       <c r="I140" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A140)*$D140</f>
-        <v>417.79367792405179</v>
+        <f t="shared" si="245"/>
+        <v>404.50560559440038</v>
       </c>
       <c r="J140" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A140)*$D140</f>
-        <v>508.07356606442295</v>
+        <f t="shared" si="246"/>
+        <v>491.91411068875959</v>
       </c>
       <c r="K140" s="16">
-        <f t="shared" si="186"/>
-        <v>4646.658620705648</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>4573.7382305883748</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
         <v>22</v>
       </c>
@@ -7047,39 +7091,39 @@
         <v>0</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" ref="D141" si="194">C141/C143</f>
+        <f t="shared" ref="D141" si="251">C141/C143</f>
         <v>0</v>
       </c>
       <c r="E141" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="241"/>
         <v>0</v>
       </c>
       <c r="F141" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="G141" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="H141" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="244"/>
         <v>0</v>
       </c>
       <c r="I141" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="J141" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A141)*$D141</f>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K141" s="16">
-        <f t="shared" si="186"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
         <v>22</v>
       </c>
@@ -7090,68 +7134,72 @@
         <v>0</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" ref="D142" si="195">C142/C143</f>
+        <f t="shared" ref="D142" si="252">C142/C143</f>
         <v>0</v>
       </c>
       <c r="E142" s="8">
-        <f>SUMIFS(P:P,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="241"/>
         <v>0</v>
       </c>
       <c r="F142" s="8">
-        <f>SUMIFS(Q:Q,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="G142" s="8">
-        <f>SUMIFS(R:R,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="H142" s="8">
-        <f>SUMIFS(S:S,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="244"/>
         <v>0</v>
       </c>
       <c r="I142" s="8">
-        <f>SUMIFS(T:T,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="J142" s="8">
-        <f>SUMIFS(U:U,$M:$M,$A142)*$D142</f>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="K142" s="17">
-        <f t="shared" si="186"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="239"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B143" s="19">
+        <f>1-D143</f>
+        <v>0</v>
+      </c>
       <c r="C143" s="3">
         <v>3186.8690000000006</v>
       </c>
       <c r="D143" s="5">
-        <f t="shared" ref="D143:E143" si="196">SUM(D134:D142)</f>
+        <f t="shared" ref="D143:E143" si="253">SUM(D134:D142)</f>
         <v>1</v>
       </c>
       <c r="E143" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="253"/>
         <v>456.81859469003371</v>
       </c>
       <c r="F143" s="9">
-        <f t="shared" ref="F143" si="197">SUM(F134:F142)</f>
-        <v>408.77707131192915</v>
+        <f t="shared" ref="F143" si="254">SUM(F134:F142)</f>
+        <v>408.77707131192921</v>
       </c>
       <c r="G143" s="9">
-        <f t="shared" ref="G143" si="198">SUM(G134:G142)</f>
-        <v>426.51310723000944</v>
+        <f t="shared" ref="G143" si="255">SUM(G134:G142)</f>
+        <v>426.5131072300095</v>
       </c>
       <c r="H143" s="9">
-        <f t="shared" ref="H143" si="199">SUM(H134:H142)</f>
+        <f t="shared" ref="H143" si="256">SUM(H134:H142)</f>
         <v>557.37420702558461</v>
       </c>
       <c r="I143" s="9">
-        <f t="shared" ref="I143" si="200">SUM(I134:I142)</f>
+        <f t="shared" ref="I143" si="257">SUM(I134:I142)</f>
         <v>565.62531938747418</v>
       </c>
       <c r="J143" s="9">
-        <f t="shared" ref="J143" si="201">SUM(J134:J142)</f>
+        <f t="shared" ref="J143" si="258">SUM(J134:J142)</f>
         <v>687.8497408229407</v>
       </c>
       <c r="K143" s="14"/>
